--- a/src/database/temp_outputs/combined_chunks_file.xlsx
+++ b/src/database/temp_outputs/combined_chunks_file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repositories\XpressCredentialling\src\database\temp_outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84364B4E-E11C-426C-B763-8A62491B1A9F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52FE6A6D-3CE5-45B2-87F4-0B4AF4E20B27}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,42 +20,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
-    <t>index</t>
+    <t>National Provider Identifier</t>
   </si>
   <si>
-    <t>npi</t>
+    <t>Name</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>email</t>
-  </si>
-  <si>
-    <t>GRANT SEARLES</t>
-  </si>
-  <si>
-    <t>grantsearles@hotmail.com</t>
-  </si>
-  <si>
-    <t>KURTIS VINSANT</t>
-  </si>
-  <si>
-    <t>ksv1203@gmail.com</t>
-  </si>
-  <si>
-    <t>JOHN MATHEWS</t>
-  </si>
-  <si>
-    <t>michelle.mcclinton@bhsala.com</t>
-  </si>
-  <si>
-    <t>DAVID MILLER</t>
-  </si>
-  <si>
-    <t>David.Miller@UTSouthwestern.edu</t>
+    <t>Email</t>
   </si>
 </sst>
 </file>
@@ -111,13 +84,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -421,16 +391,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.88671875" customWidth="1"/>
-    <col min="2" max="2" width="42.5546875" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" customWidth="1"/>
-    <col min="4" max="4" width="34" customWidth="1"/>
+    <col min="1" max="1" width="22.77734375" customWidth="1"/>
+    <col min="2" max="2" width="35.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -440,65 +408,6 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2">
-        <v>1427085877</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2">
-        <v>1144257882</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2">
-        <v>1689630188</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2">
-        <v>1497844617</v>
-      </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/src/database/temp_outputs/combined_chunks_file.xlsx
+++ b/src/database/temp_outputs/combined_chunks_file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repositories\XpressCredentialling\src\database\temp_outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52FE6A6D-3CE5-45B2-87F4-0B4AF4E20B27}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B15B666A-94CC-4A23-8D81-48DE5DA4D458}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="890">
   <si>
     <t>National Provider Identifier</t>
   </si>
@@ -29,6 +29,2667 @@
   </si>
   <si>
     <t>Email</t>
+  </si>
+  <si>
+    <t>1376567099</t>
+  </si>
+  <si>
+    <t>ADRIAN PARK</t>
+  </si>
+  <si>
+    <t>apark0111@gmail.com</t>
+  </si>
+  <si>
+    <t>1427085877</t>
+  </si>
+  <si>
+    <t>GRANT SEARLES</t>
+  </si>
+  <si>
+    <t>grantsearles@hotmail.com</t>
+  </si>
+  <si>
+    <t>1215987417</t>
+  </si>
+  <si>
+    <t>ALEJANDRO GANDSAS</t>
+  </si>
+  <si>
+    <t>agandsas@luminishealth.org</t>
+  </si>
+  <si>
+    <t>1306809033</t>
+  </si>
+  <si>
+    <t>PETER LIAO</t>
+  </si>
+  <si>
+    <t>peter.liao@centerforvein.com</t>
+  </si>
+  <si>
+    <t>1063451714</t>
+  </si>
+  <si>
+    <t>LISA JACOBS</t>
+  </si>
+  <si>
+    <t>kviands1@jhmi.edu</t>
+  </si>
+  <si>
+    <t>1497844617</t>
+  </si>
+  <si>
+    <t>DAVID MILLER</t>
+  </si>
+  <si>
+    <t>David.Miller@UTSouthwestern.edu</t>
+  </si>
+  <si>
+    <t>1831114511</t>
+  </si>
+  <si>
+    <t>KARL RIGGLE</t>
+  </si>
+  <si>
+    <t>drriggle@tssurg.net</t>
+  </si>
+  <si>
+    <t>1689630188</t>
+  </si>
+  <si>
+    <t>JOHN MATHEWS</t>
+  </si>
+  <si>
+    <t>michelle.mcclinton@bhsala.com</t>
+  </si>
+  <si>
+    <t>1578585683</t>
+  </si>
+  <si>
+    <t>BENJAMIN PHILOSOPHE</t>
+  </si>
+  <si>
+    <t>bphilosophe@gmail.com</t>
+  </si>
+  <si>
+    <t>1891754370</t>
+  </si>
+  <si>
+    <t>JULIE BIELEC</t>
+  </si>
+  <si>
+    <t>bielecjf@upmc.edu</t>
+  </si>
+  <si>
+    <t>1770519761</t>
+  </si>
+  <si>
+    <t>CHRISTOPHER WOLFGANG</t>
+  </si>
+  <si>
+    <t>trish.mcginty@nyulangone.org</t>
+  </si>
+  <si>
+    <t>1265631352</t>
+  </si>
+  <si>
+    <t>KARTIKEY PANDYA</t>
+  </si>
+  <si>
+    <t>kartikey.pandya@mainehealth.org</t>
+  </si>
+  <si>
+    <t>1851540108</t>
+  </si>
+  <si>
+    <t>KHALDOUN BEKDACHE</t>
+  </si>
+  <si>
+    <t>khaldounbekdache@gmail.com</t>
+  </si>
+  <si>
+    <t>1255485876</t>
+  </si>
+  <si>
+    <t>STEVEN FLOERCHINGER</t>
+  </si>
+  <si>
+    <t>steve@ponderafarm.com</t>
+  </si>
+  <si>
+    <t>1598732042</t>
+  </si>
+  <si>
+    <t>PAMELA GRUCHACZ</t>
+  </si>
+  <si>
+    <t>pamela.gruchaczz@gmail.com</t>
+  </si>
+  <si>
+    <t>1922054626</t>
+  </si>
+  <si>
+    <t>BENJAMIN MILLER</t>
+  </si>
+  <si>
+    <t>mill1490@gmail.com</t>
+  </si>
+  <si>
+    <t>1518935972</t>
+  </si>
+  <si>
+    <t>TIMOTHY FITZGERALD</t>
+  </si>
+  <si>
+    <t>tlfitzgera@mmc.org</t>
+  </si>
+  <si>
+    <t>1710991229</t>
+  </si>
+  <si>
+    <t>DAVID KING</t>
+  </si>
+  <si>
+    <t>dking@cpgh.org</t>
+  </si>
+  <si>
+    <t>1366404600</t>
+  </si>
+  <si>
+    <t>MICHAEL TODD</t>
+  </si>
+  <si>
+    <t>chinook@gci.net</t>
+  </si>
+  <si>
+    <t>1922142819</t>
+  </si>
+  <si>
+    <t>ASHOK RAI</t>
+  </si>
+  <si>
+    <t>araimd.facs@gmail.com</t>
+  </si>
+  <si>
+    <t>1215090832</t>
+  </si>
+  <si>
+    <t>DEAN KIM</t>
+  </si>
+  <si>
+    <t>cmonaco1@hfhs.org</t>
+  </si>
+  <si>
+    <t>1003995713</t>
+  </si>
+  <si>
+    <t>TAK MING KO</t>
+  </si>
+  <si>
+    <t>tfidko@gmail.com</t>
+  </si>
+  <si>
+    <t>1194775205</t>
+  </si>
+  <si>
+    <t>THOMAS ROHS</t>
+  </si>
+  <si>
+    <t>thomasrohs65@gmail.com</t>
+  </si>
+  <si>
+    <t>1841321890</t>
+  </si>
+  <si>
+    <t>TIMOTHY TESLOW</t>
+  </si>
+  <si>
+    <t>teslowt@yahoo.com</t>
+  </si>
+  <si>
+    <t>1568474195</t>
+  </si>
+  <si>
+    <t>MICHAEL JACOBS</t>
+  </si>
+  <si>
+    <t>mjjacobsmd@gmail.com</t>
+  </si>
+  <si>
+    <t>1194761924</t>
+  </si>
+  <si>
+    <t>ANDREW GORDON</t>
+  </si>
+  <si>
+    <t>andrew8900@gmail.com</t>
+  </si>
+  <si>
+    <t>1083775407</t>
+  </si>
+  <si>
+    <t>LAURA DALLA VECCHIA</t>
+  </si>
+  <si>
+    <t>ldallavecchia@comcast.net</t>
+  </si>
+  <si>
+    <t>1447228606</t>
+  </si>
+  <si>
+    <t>WILLIAM MONTANO</t>
+  </si>
+  <si>
+    <t>montano@acsalaska.net</t>
+  </si>
+  <si>
+    <t>1558310912</t>
+  </si>
+  <si>
+    <t>RONALD FORD</t>
+  </si>
+  <si>
+    <t>ronald.ford@corewellhealth.org</t>
+  </si>
+  <si>
+    <t>1922026822</t>
+  </si>
+  <si>
+    <t>JEFFREY HANNON</t>
+  </si>
+  <si>
+    <t>robinreynolds@sampadocs.com</t>
+  </si>
+  <si>
+    <t>1376500496</t>
+  </si>
+  <si>
+    <t>SUSAN SEMAN</t>
+  </si>
+  <si>
+    <t>ssemandoc@gmail.com</t>
+  </si>
+  <si>
+    <t>1275521510</t>
+  </si>
+  <si>
+    <t>DENNIS FERNANDEZ</t>
+  </si>
+  <si>
+    <t>DennisFernandezMD@gmail.com</t>
+  </si>
+  <si>
+    <t>1316911498</t>
+  </si>
+  <si>
+    <t>JAMES LULEK</t>
+  </si>
+  <si>
+    <t>karen.arning@corewellhealth.org</t>
+  </si>
+  <si>
+    <t>1285608588</t>
+  </si>
+  <si>
+    <t>REX SHERER</t>
+  </si>
+  <si>
+    <t>rsherer777@mindspring.com</t>
+  </si>
+  <si>
+    <t>1912982141</t>
+  </si>
+  <si>
+    <t>PATRICK BOSARGE</t>
+  </si>
+  <si>
+    <t>bosarge.md@gmail.com</t>
+  </si>
+  <si>
+    <t>1841250156</t>
+  </si>
+  <si>
+    <t>JOHN ROBERTSON</t>
+  </si>
+  <si>
+    <t>john.robertson@providence.org</t>
+  </si>
+  <si>
+    <t>1831128180</t>
+  </si>
+  <si>
+    <t>JOHN MARTIN</t>
+  </si>
+  <si>
+    <t>suzie.smeaton@atriumhealth.org</t>
+  </si>
+  <si>
+    <t>1942249727</t>
+  </si>
+  <si>
+    <t>MARK DITTENBIR</t>
+  </si>
+  <si>
+    <t>amaddogrby@aol.com</t>
+  </si>
+  <si>
+    <t>1669427753</t>
+  </si>
+  <si>
+    <t>PAULA RECHNER</t>
+  </si>
+  <si>
+    <t>paula.rechner@mymichigan.org</t>
+  </si>
+  <si>
+    <t>1982644639</t>
+  </si>
+  <si>
+    <t>EDWARD KRESKE</t>
+  </si>
+  <si>
+    <t>ekreske1966@gmail.com</t>
+  </si>
+  <si>
+    <t>1134290984</t>
+  </si>
+  <si>
+    <t>JUSTIN MOELLINGER</t>
+  </si>
+  <si>
+    <t>jmoellinger@hotmail.com</t>
+  </si>
+  <si>
+    <t>1154765493</t>
+  </si>
+  <si>
+    <t>STEVEN SKUBE</t>
+  </si>
+  <si>
+    <t>Sjskube@gmail.com</t>
+  </si>
+  <si>
+    <t>1437476876</t>
+  </si>
+  <si>
+    <t>SARA WILDENBERG</t>
+  </si>
+  <si>
+    <t>swilden1@fairview.org</t>
+  </si>
+  <si>
+    <t>1043279797</t>
+  </si>
+  <si>
+    <t>KEVIN COTTINGHAM</t>
+  </si>
+  <si>
+    <t>kmcot@bellsouth.net</t>
+  </si>
+  <si>
+    <t>1013295260</t>
+  </si>
+  <si>
+    <t>ZACHARY ERNST</t>
+  </si>
+  <si>
+    <t>zachnlinds@msn.com</t>
+  </si>
+  <si>
+    <t>1720079940</t>
+  </si>
+  <si>
+    <t>SETH RAYBURN</t>
+  </si>
+  <si>
+    <t>srayburn01@hotmail.com</t>
+  </si>
+  <si>
+    <t>1366680720</t>
+  </si>
+  <si>
+    <t>MEGAN NELSON</t>
+  </si>
+  <si>
+    <t>pederson.cathy@mayo.edu</t>
+  </si>
+  <si>
+    <t>1417042136</t>
+  </si>
+  <si>
+    <t>JUAN CAMPOS</t>
+  </si>
+  <si>
+    <t>jcv67@hotmail.com</t>
+  </si>
+  <si>
+    <t>1457448219</t>
+  </si>
+  <si>
+    <t>RICHARD HWANG</t>
+  </si>
+  <si>
+    <t>ryeuphwang@gmail.com</t>
+  </si>
+  <si>
+    <t>1992097703</t>
+  </si>
+  <si>
+    <t>GREGORY GERRISH</t>
+  </si>
+  <si>
+    <t>greg.gerrishmd@gmail.com</t>
+  </si>
+  <si>
+    <t>1457392045</t>
+  </si>
+  <si>
+    <t>JOHN YOUNG</t>
+  </si>
+  <si>
+    <t>jisaacyoung@gmail.com</t>
+  </si>
+  <si>
+    <t>1356389803</t>
+  </si>
+  <si>
+    <t>RAVINDRA MAILAPUR</t>
+  </si>
+  <si>
+    <t>ravim@icloud.com</t>
+  </si>
+  <si>
+    <t>1639175029</t>
+  </si>
+  <si>
+    <t>MICHAEL DE PRIEST</t>
+  </si>
+  <si>
+    <t>Michael.DeCillia@bbsalz.at</t>
+  </si>
+  <si>
+    <t>1992723472</t>
+  </si>
+  <si>
+    <t>JOHN MAZUSKI</t>
+  </si>
+  <si>
+    <t>johmaz@yahoo.com</t>
+  </si>
+  <si>
+    <t>1720069230</t>
+  </si>
+  <si>
+    <t>DONALD MARTIN</t>
+  </si>
+  <si>
+    <t>dmartin@tc3net.com</t>
+  </si>
+  <si>
+    <t>1962519785</t>
+  </si>
+  <si>
+    <t>CRAIG SMITH</t>
+  </si>
+  <si>
+    <t>csmith@ssainc.net</t>
+  </si>
+  <si>
+    <t>1881894673</t>
+  </si>
+  <si>
+    <t>CHRISTOPHER MENENDEZ</t>
+  </si>
+  <si>
+    <t>chrismdez@gmail.com</t>
+  </si>
+  <si>
+    <t>1730220286</t>
+  </si>
+  <si>
+    <t>STEVEN GROSSO</t>
+  </si>
+  <si>
+    <t>steve@yellowstoneplasticsurgery.com</t>
+  </si>
+  <si>
+    <t>1144541210</t>
+  </si>
+  <si>
+    <t>JAMES HEAD</t>
+  </si>
+  <si>
+    <t>stacy.potter@commonspirit.org</t>
+  </si>
+  <si>
+    <t>1205830684</t>
+  </si>
+  <si>
+    <t>DANIEL PARA</t>
+  </si>
+  <si>
+    <t>DrDanPara@gmail.com</t>
+  </si>
+  <si>
+    <t>1568468601</t>
+  </si>
+  <si>
+    <t>SUSAN CORTESI</t>
+  </si>
+  <si>
+    <t>scortesi@azadvanced.com</t>
+  </si>
+  <si>
+    <t>1134154941</t>
+  </si>
+  <si>
+    <t>DEVIN GRAY</t>
+  </si>
+  <si>
+    <t>devinlynngray@gmail.com</t>
+  </si>
+  <si>
+    <t>1548323835</t>
+  </si>
+  <si>
+    <t>ELIZABETH SUH</t>
+  </si>
+  <si>
+    <t>esuh@communitymed.org</t>
+  </si>
+  <si>
+    <t>1508980582</t>
+  </si>
+  <si>
+    <t>SCOTT ELLIS</t>
+  </si>
+  <si>
+    <t>sellisons@yahoo.com</t>
+  </si>
+  <si>
+    <t>1124061411</t>
+  </si>
+  <si>
+    <t>WILLIAM HUVAL</t>
+  </si>
+  <si>
+    <t>tval140@gmail.com</t>
+  </si>
+  <si>
+    <t>1174521819</t>
+  </si>
+  <si>
+    <t>ALBERT RIZZO</t>
+  </si>
+  <si>
+    <t>rizmdsurgeon@yahoo.com</t>
+  </si>
+  <si>
+    <t>1053321265</t>
+  </si>
+  <si>
+    <t>RYAN GUNLIKSON</t>
+  </si>
+  <si>
+    <t>ryangunlikson@gmail.com</t>
+  </si>
+  <si>
+    <t>1306853130</t>
+  </si>
+  <si>
+    <t>BRET MURRAY</t>
+  </si>
+  <si>
+    <t>btmcmorrow@yahoo.com</t>
+  </si>
+  <si>
+    <t>1437127073</t>
+  </si>
+  <si>
+    <t>BRUCE DAVIS</t>
+  </si>
+  <si>
+    <t>brdavis@honorhealth.com</t>
+  </si>
+  <si>
+    <t>1982650768</t>
+  </si>
+  <si>
+    <t>AMY MARTIN</t>
+  </si>
+  <si>
+    <t>GALEOAJ@MSN.COM</t>
+  </si>
+  <si>
+    <t>1346276516</t>
+  </si>
+  <si>
+    <t>DEBRA KONTNY</t>
+  </si>
+  <si>
+    <t>drkontny@aol.com</t>
+  </si>
+  <si>
+    <t>1952384018</t>
+  </si>
+  <si>
+    <t>EUGENE POWELL</t>
+  </si>
+  <si>
+    <t>powell100us@yahoo.com</t>
+  </si>
+  <si>
+    <t>1720099401</t>
+  </si>
+  <si>
+    <t>ROBIN BLACKSTONE</t>
+  </si>
+  <si>
+    <t>Robin.Blackstone@BlackstoneHealth.com</t>
+  </si>
+  <si>
+    <t>1174529200</t>
+  </si>
+  <si>
+    <t>LAWRENCE DAMORE</t>
+  </si>
+  <si>
+    <t>ljdamore@cox.net</t>
+  </si>
+  <si>
+    <t>1992930192</t>
+  </si>
+  <si>
+    <t>CHIRAG DESAI</t>
+  </si>
+  <si>
+    <t>csdesai@gmail.com</t>
+  </si>
+  <si>
+    <t>1053360016</t>
+  </si>
+  <si>
+    <t>GREGORY DELLA ROCCA</t>
+  </si>
+  <si>
+    <t>kns3n3@heatlh.missouri.edu</t>
+  </si>
+  <si>
+    <t>1801043930</t>
+  </si>
+  <si>
+    <t>KAREN SHERMAN</t>
+  </si>
+  <si>
+    <t>sharena.sutton@duke.edu</t>
+  </si>
+  <si>
+    <t>1114005253</t>
+  </si>
+  <si>
+    <t>MICHAEL MILLER</t>
+  </si>
+  <si>
+    <t>mijomi1083@outlook.com</t>
+  </si>
+  <si>
+    <t>1558367235</t>
+  </si>
+  <si>
+    <t>MATTHEW ALTER</t>
+  </si>
+  <si>
+    <t>mattalter78@gmail.com</t>
+  </si>
+  <si>
+    <t>1508850116</t>
+  </si>
+  <si>
+    <t>MUHAMMAD KHAN</t>
+  </si>
+  <si>
+    <t>drjkhan72@yahoo.com</t>
+  </si>
+  <si>
+    <t>1225093529</t>
+  </si>
+  <si>
+    <t>DAVID SPENCER</t>
+  </si>
+  <si>
+    <t>dmspen616@gmail.com</t>
+  </si>
+  <si>
+    <t>1821055138</t>
+  </si>
+  <si>
+    <t>BRENT BRUDERER</t>
+  </si>
+  <si>
+    <t>brent.bruderer@va.gov</t>
+  </si>
+  <si>
+    <t>1164450367</t>
+  </si>
+  <si>
+    <t>RICHARD HARDING</t>
+  </si>
+  <si>
+    <t>rhardingmd@gmail.com</t>
+  </si>
+  <si>
+    <t>1932170057</t>
+  </si>
+  <si>
+    <t>DAVID SCHALL</t>
+  </si>
+  <si>
+    <t>david.g.schall@gmail.com</t>
+  </si>
+  <si>
+    <t>1013952464</t>
+  </si>
+  <si>
+    <t>JAMES BALSERAK</t>
+  </si>
+  <si>
+    <t>jcbalserakmd@gmail.com</t>
+  </si>
+  <si>
+    <t>1053417840</t>
+  </si>
+  <si>
+    <t>WAYNE ANDERSON</t>
+  </si>
+  <si>
+    <t>wayne.anderson@commonspirit.org</t>
+  </si>
+  <si>
+    <t>1740240712</t>
+  </si>
+  <si>
+    <t>ANDREW SMITH</t>
+  </si>
+  <si>
+    <t>ahsmith918@gmail.com</t>
+  </si>
+  <si>
+    <t>1467411140</t>
+  </si>
+  <si>
+    <t>VENKATA EVANI</t>
+  </si>
+  <si>
+    <t>wlvrne@cox.net</t>
+  </si>
+  <si>
+    <t>1730138561</t>
+  </si>
+  <si>
+    <t>TRAVIS HOLCOMBE</t>
+  </si>
+  <si>
+    <t>sarah@holcombemd.com</t>
+  </si>
+  <si>
+    <t>1275561649</t>
+  </si>
+  <si>
+    <t>PAUL WASEMILLER</t>
+  </si>
+  <si>
+    <t>pswase@gmail.com</t>
+  </si>
+  <si>
+    <t>1356336358</t>
+  </si>
+  <si>
+    <t>MICHAEL BOUTON</t>
+  </si>
+  <si>
+    <t>msbouton@sbcglobal.net</t>
+  </si>
+  <si>
+    <t>1295938413</t>
+  </si>
+  <si>
+    <t>BRANDON HELBLING</t>
+  </si>
+  <si>
+    <t>bhelbling1@gmail.com</t>
+  </si>
+  <si>
+    <t>1376753459</t>
+  </si>
+  <si>
+    <t>ENEJ GASEVIC</t>
+  </si>
+  <si>
+    <t>ENEJ.GASEVIC@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>1437320710</t>
+  </si>
+  <si>
+    <t>KHALED ZREIK</t>
+  </si>
+  <si>
+    <t>khaled.zreik@sanfordhealth.org</t>
+  </si>
+  <si>
+    <t>1659507861</t>
+  </si>
+  <si>
+    <t>KIMBERLY STONE</t>
+  </si>
+  <si>
+    <t>mnugent@stanford.edu</t>
+  </si>
+  <si>
+    <t>1508942897</t>
+  </si>
+  <si>
+    <t>DEREK KANE</t>
+  </si>
+  <si>
+    <t>derekdkane@yahoo.com</t>
+  </si>
+  <si>
+    <t>1437386109</t>
+  </si>
+  <si>
+    <t>BRAD OLBERDING</t>
+  </si>
+  <si>
+    <t>sheila@gsalincoln.com</t>
+  </si>
+  <si>
+    <t>1336376284</t>
+  </si>
+  <si>
+    <t>JEREMY ALBIN</t>
+  </si>
+  <si>
+    <t>jeremyalbin@yahoo.com</t>
+  </si>
+  <si>
+    <t>1306074034</t>
+  </si>
+  <si>
+    <t>STEVE CHOE</t>
+  </si>
+  <si>
+    <t>schoes@gmail.com</t>
+  </si>
+  <si>
+    <t>1366417305</t>
+  </si>
+  <si>
+    <t>KRISTEN ENGLE</t>
+  </si>
+  <si>
+    <t>kenglemd@gmail.com</t>
+  </si>
+  <si>
+    <t>1497984033</t>
+  </si>
+  <si>
+    <t>TIFFANY TANNER</t>
+  </si>
+  <si>
+    <t>lbadami@unmc.edu</t>
+  </si>
+  <si>
+    <t>1831191956</t>
+  </si>
+  <si>
+    <t>DANNY COLTON</t>
+  </si>
+  <si>
+    <t>danny.m.colton@hhs.sccgov.org</t>
+  </si>
+  <si>
+    <t>1073837639</t>
+  </si>
+  <si>
+    <t>CALEB SCHROEDER</t>
+  </si>
+  <si>
+    <t>hjoweidner@gmail.com</t>
+  </si>
+  <si>
+    <t>1962456871</t>
+  </si>
+  <si>
+    <t>DAVID CORNELL</t>
+  </si>
+  <si>
+    <t>David.Cornell@TrinityHealthofNE.org</t>
+  </si>
+  <si>
+    <t>1215266770</t>
+  </si>
+  <si>
+    <t>ERIC KUBAT</t>
+  </si>
+  <si>
+    <t>erickubat@gmail.com</t>
+  </si>
+  <si>
+    <t>1588955694</t>
+  </si>
+  <si>
+    <t>PETER PAK</t>
+  </si>
+  <si>
+    <t>petersungjinpak@gmail.com</t>
+  </si>
+  <si>
+    <t>1467606590</t>
+  </si>
+  <si>
+    <t>SHANNON WONG</t>
+  </si>
+  <si>
+    <t>rebecca.dugger@unmc.edu</t>
+  </si>
+  <si>
+    <t>1780885202</t>
+  </si>
+  <si>
+    <t>MEGAN FULLER</t>
+  </si>
+  <si>
+    <t>megkfuller@gmail.com</t>
+  </si>
+  <si>
+    <t>1003832254</t>
+  </si>
+  <si>
+    <t>BRETT WAIBEL</t>
+  </si>
+  <si>
+    <t>cramers@unmc.edu</t>
+  </si>
+  <si>
+    <t>1952416422</t>
+  </si>
+  <si>
+    <t>THOMAS MOORE</t>
+  </si>
+  <si>
+    <t>thomas.l.moore@comcast.net</t>
+  </si>
+  <si>
+    <t>1669442737</t>
+  </si>
+  <si>
+    <t>SAMUEL GERBER</t>
+  </si>
+  <si>
+    <t>Gerbersd@gmail.com</t>
+  </si>
+  <si>
+    <t>1124135348</t>
+  </si>
+  <si>
+    <t>STEVEN KIM</t>
+  </si>
+  <si>
+    <t>steven.charles.kim@emory.edu</t>
+  </si>
+  <si>
+    <t>1750359642</t>
+  </si>
+  <si>
+    <t>ROBERT WILCOX</t>
+  </si>
+  <si>
+    <t>doctorbobwilcox@gmail.com</t>
+  </si>
+  <si>
+    <t>1396740858</t>
+  </si>
+  <si>
+    <t>MICHAEL NAPIERKOWSKI</t>
+  </si>
+  <si>
+    <t>Michael.T.Napierkowski@kp.org</t>
+  </si>
+  <si>
+    <t>1992798904</t>
+  </si>
+  <si>
+    <t>PATRICK MAHON</t>
+  </si>
+  <si>
+    <t>Patrick.Mahon@cmc-nh.org</t>
+  </si>
+  <si>
+    <t>1508859083</t>
+  </si>
+  <si>
+    <t>DAVID WONG</t>
+  </si>
+  <si>
+    <t>mendozao@calmeddocs.com</t>
+  </si>
+  <si>
+    <t>1043283799</t>
+  </si>
+  <si>
+    <t>MICHAEL REMAR</t>
+  </si>
+  <si>
+    <t>mremar@icloud.com</t>
+  </si>
+  <si>
+    <t>1114951753</t>
+  </si>
+  <si>
+    <t>MICHAEL ORMONT</t>
+  </si>
+  <si>
+    <t>michael.ormont@gmail.com</t>
+  </si>
+  <si>
+    <t>1568774222</t>
+  </si>
+  <si>
+    <t>MARIUS CALIN</t>
+  </si>
+  <si>
+    <t>calinmariusliviu@yahoo.com</t>
+  </si>
+  <si>
+    <t>1922242247</t>
+  </si>
+  <si>
+    <t>JOYCE BONITZ</t>
+  </si>
+  <si>
+    <t>joycebonitz@gmail.com</t>
+  </si>
+  <si>
+    <t>1407852619</t>
+  </si>
+  <si>
+    <t>MICHAEL FRATERELLI</t>
+  </si>
+  <si>
+    <t>sca@surgicalconsultantsaurora.com</t>
+  </si>
+  <si>
+    <t>1477596062</t>
+  </si>
+  <si>
+    <t>MICHAEL SNYDER</t>
+  </si>
+  <si>
+    <t>mjsnyder98@att.net</t>
+  </si>
+  <si>
+    <t>1316364144</t>
+  </si>
+  <si>
+    <t>DINA GALAKTIONOVA</t>
+  </si>
+  <si>
+    <t>Dgalakti@gmail.com</t>
+  </si>
+  <si>
+    <t>1508992355</t>
+  </si>
+  <si>
+    <t>MELANIA YEATS</t>
+  </si>
+  <si>
+    <t>melania_y@hotmail.com</t>
+  </si>
+  <si>
+    <t>1871555102</t>
+  </si>
+  <si>
+    <t>CHRIS WINTER</t>
+  </si>
+  <si>
+    <t>cdrcbw@hotmail.com</t>
+  </si>
+  <si>
+    <t>1932111895</t>
+  </si>
+  <si>
+    <t>LINDA SMITH</t>
+  </si>
+  <si>
+    <t>rosalind@lindasmithmd.com</t>
+  </si>
+  <si>
+    <t>1447267018</t>
+  </si>
+  <si>
+    <t>STEPHEN BARNES</t>
+  </si>
+  <si>
+    <t>barnesste@health.missouri.edu</t>
+  </si>
+  <si>
+    <t>1396731899</t>
+  </si>
+  <si>
+    <t>JON LEVIN</t>
+  </si>
+  <si>
+    <t>jonathanlevine19@gmail.com</t>
+  </si>
+  <si>
+    <t>1538165147</t>
+  </si>
+  <si>
+    <t>WILLIAM POLLARD</t>
+  </si>
+  <si>
+    <t>william.pollard@christushealth.org</t>
+  </si>
+  <si>
+    <t>1710993803</t>
+  </si>
+  <si>
+    <t>SUSAN SEEDMAN</t>
+  </si>
+  <si>
+    <t>drseedman@swcp.com</t>
+  </si>
+  <si>
+    <t>1992818140</t>
+  </si>
+  <si>
+    <t>CLAY BURLEW</t>
+  </si>
+  <si>
+    <t>clay.burlew@cuanschutz.edu</t>
+  </si>
+  <si>
+    <t>1992712947</t>
+  </si>
+  <si>
+    <t>JOHN RUSSELL</t>
+  </si>
+  <si>
+    <t>bpierce@salud.unm.edu</t>
+  </si>
+  <si>
+    <t>1639286123</t>
+  </si>
+  <si>
+    <t>SHARMILA DISSANAIKE</t>
+  </si>
+  <si>
+    <t>sdissanaike@salud.unm.edu</t>
+  </si>
+  <si>
+    <t>1780681999</t>
+  </si>
+  <si>
+    <t>SALLIE CLARK</t>
+  </si>
+  <si>
+    <t>1992708515</t>
+  </si>
+  <si>
+    <t>NIKHIL MEHTA</t>
+  </si>
+  <si>
+    <t>nshroffmehta@gmail.com</t>
+  </si>
+  <si>
+    <t>1871539627</t>
+  </si>
+  <si>
+    <t>DAVID BECK</t>
+  </si>
+  <si>
+    <t>dbecker@challiance.org</t>
+  </si>
+  <si>
+    <t>1578558219</t>
+  </si>
+  <si>
+    <t>AKBAR ALI</t>
+  </si>
+  <si>
+    <t>akbarali1998@gmail.com</t>
+  </si>
+  <si>
+    <t>1538252416</t>
+  </si>
+  <si>
+    <t>FRANK CHAE</t>
+  </si>
+  <si>
+    <t>frank.chae@hcahealthone.com</t>
+  </si>
+  <si>
+    <t>1013937390</t>
+  </si>
+  <si>
+    <t>RICHARD MOUCHANTAT</t>
+  </si>
+  <si>
+    <t>mouchantat@comcast.net</t>
+  </si>
+  <si>
+    <t>1700817434</t>
+  </si>
+  <si>
+    <t>LISA BALDUF</t>
+  </si>
+  <si>
+    <t>lbalduf@hotmail.com</t>
+  </si>
+  <si>
+    <t>1972762581</t>
+  </si>
+  <si>
+    <t>MICHAEL ALPEROVICH</t>
+  </si>
+  <si>
+    <t>alperovich@gmail.com</t>
+  </si>
+  <si>
+    <t>1740437904</t>
+  </si>
+  <si>
+    <t>DARREN SMITH</t>
+  </si>
+  <si>
+    <t>dms1717@gmail.com</t>
+  </si>
+  <si>
+    <t>1205103942</t>
+  </si>
+  <si>
+    <t>JACQUELINE TSAI</t>
+  </si>
+  <si>
+    <t>tsaija@gmail.com</t>
+  </si>
+  <si>
+    <t>1669623328</t>
+  </si>
+  <si>
+    <t>TONI BENINATO</t>
+  </si>
+  <si>
+    <t>toni.beninato@gmail.com</t>
+  </si>
+  <si>
+    <t>1699095513</t>
+  </si>
+  <si>
+    <t>BRUNA BABIC</t>
+  </si>
+  <si>
+    <t>bbabic@gmail.com</t>
+  </si>
+  <si>
+    <t>1609806090</t>
+  </si>
+  <si>
+    <t>SHERRY MELTON</t>
+  </si>
+  <si>
+    <t>smmelton053@gmail.com</t>
+  </si>
+  <si>
+    <t>1518279124</t>
+  </si>
+  <si>
+    <t>VALERIE BRUTUS</t>
+  </si>
+  <si>
+    <t>Valerie.Brutus@hhchealth.org</t>
+  </si>
+  <si>
+    <t>1295996205</t>
+  </si>
+  <si>
+    <t>YONG KWON</t>
+  </si>
+  <si>
+    <t>yong.kwon@utsouthwestern.edu</t>
+  </si>
+  <si>
+    <t>1043240997</t>
+  </si>
+  <si>
+    <t>FRANCIS LEE</t>
+  </si>
+  <si>
+    <t>francisslee1@icloud.com</t>
+  </si>
+  <si>
+    <t>1497856678</t>
+  </si>
+  <si>
+    <t>NORMA SMALLS</t>
+  </si>
+  <si>
+    <t>drnormasmalls@gmail.com</t>
+  </si>
+  <si>
+    <t>1801871306</t>
+  </si>
+  <si>
+    <t>BARRY LOSASSO</t>
+  </si>
+  <si>
+    <t>info@pediatricsurgical.net</t>
+  </si>
+  <si>
+    <t>1477674562</t>
+  </si>
+  <si>
+    <t>KONSTANTINOS SPANIOLAS</t>
+  </si>
+  <si>
+    <t>konstantinos.spaniolas@stonybrookmedicine.edu</t>
+  </si>
+  <si>
+    <t>1649582214</t>
+  </si>
+  <si>
+    <t>CANDICE CHIPMAN</t>
+  </si>
+  <si>
+    <t>crchipman@gmail.com</t>
+  </si>
+  <si>
+    <t>1699071183</t>
+  </si>
+  <si>
+    <t>KATE TWELKER</t>
+  </si>
+  <si>
+    <t>kt2098@nyu.edu</t>
+  </si>
+  <si>
+    <t>1124253935</t>
+  </si>
+  <si>
+    <t>ANNE STEY</t>
+  </si>
+  <si>
+    <t>as013j@gmail.com</t>
+  </si>
+  <si>
+    <t>1831118868</t>
+  </si>
+  <si>
+    <t>MARK JOHNSON</t>
+  </si>
+  <si>
+    <t>markjmd@gmail.com</t>
+  </si>
+  <si>
+    <t>1356445837</t>
+  </si>
+  <si>
+    <t>BRENT BOGARD</t>
+  </si>
+  <si>
+    <t>b-bogard@sbcglobal.net</t>
+  </si>
+  <si>
+    <t>1881777811</t>
+  </si>
+  <si>
+    <t>JOHN WILCHER</t>
+  </si>
+  <si>
+    <t>jswilcher@gmail.com</t>
+  </si>
+  <si>
+    <t>1912001538</t>
+  </si>
+  <si>
+    <t>TIMOTHY BARNETT</t>
+  </si>
+  <si>
+    <t>trbarnettmd@yahoo.com</t>
+  </si>
+  <si>
+    <t>1588605356</t>
+  </si>
+  <si>
+    <t>WILLIAM PURKERT</t>
+  </si>
+  <si>
+    <t>william.purkert@inova.org</t>
+  </si>
+  <si>
+    <t>1285739755</t>
+  </si>
+  <si>
+    <t>1619963139</t>
+  </si>
+  <si>
+    <t>AMIR MOAZZEZ</t>
+  </si>
+  <si>
+    <t>Amirmoazzez@hotmail.com</t>
+  </si>
+  <si>
+    <t>1710908173</t>
+  </si>
+  <si>
+    <t>JAMES COOK</t>
+  </si>
+  <si>
+    <t>jcook5188@gmail.com</t>
+  </si>
+  <si>
+    <t>1366437493</t>
+  </si>
+  <si>
+    <t>GEORGE KARTALIAN, JR.</t>
+  </si>
+  <si>
+    <t>thekkekandathil@yahoo.com</t>
+  </si>
+  <si>
+    <t>1134205057</t>
+  </si>
+  <si>
+    <t>FREDERICK WATKINS</t>
+  </si>
+  <si>
+    <t>tedwatkins303@gmail.com</t>
+  </si>
+  <si>
+    <t>1013915651</t>
+  </si>
+  <si>
+    <t>SARABJIT ANAND</t>
+  </si>
+  <si>
+    <t>sarabanand@hotmail.com</t>
+  </si>
+  <si>
+    <t>1073537635</t>
+  </si>
+  <si>
+    <t>SAEED MAREFAT</t>
+  </si>
+  <si>
+    <t>drmarefat@drmarefat.com</t>
+  </si>
+  <si>
+    <t>1720073463</t>
+  </si>
+  <si>
+    <t>KHALIQUE ZAHIR</t>
+  </si>
+  <si>
+    <t>geraldine@zahircosmetics.com</t>
+  </si>
+  <si>
+    <t>1700046737</t>
+  </si>
+  <si>
+    <t>JEREMY JOHNSON</t>
+  </si>
+  <si>
+    <t>susan-cloer@ouhsc.edu</t>
+  </si>
+  <si>
+    <t>1679899421</t>
+  </si>
+  <si>
+    <t>RACHEL TYLER</t>
+  </si>
+  <si>
+    <t>rachel.tyler@ascension.org</t>
+  </si>
+  <si>
+    <t>1306969738</t>
+  </si>
+  <si>
+    <t>ROBERT MARSH</t>
+  </si>
+  <si>
+    <t>remarshmd@gmail.com</t>
+  </si>
+  <si>
+    <t>1851318885</t>
+  </si>
+  <si>
+    <t>MARC RICKFORD</t>
+  </si>
+  <si>
+    <t>mrickford@gmail.com</t>
+  </si>
+  <si>
+    <t>1033422332</t>
+  </si>
+  <si>
+    <t>MARK SCHWARTZ</t>
+  </si>
+  <si>
+    <t>markschwartzmd@gmail.com</t>
+  </si>
+  <si>
+    <t>1659319747</t>
+  </si>
+  <si>
+    <t>ARUN CHOWLA</t>
+  </si>
+  <si>
+    <t>novasurgery@gmail.com</t>
+  </si>
+  <si>
+    <t>1396063392</t>
+  </si>
+  <si>
+    <t>LAURA FISCHER</t>
+  </si>
+  <si>
+    <t>lfischer22@yahoo.com</t>
+  </si>
+  <si>
+    <t>1023452596</t>
+  </si>
+  <si>
+    <t>MARY LINDEMUTH</t>
+  </si>
+  <si>
+    <t>marylindemuth@gmail.com</t>
+  </si>
+  <si>
+    <t>1023455508</t>
+  </si>
+  <si>
+    <t>WILLY BUSTINZA FARFAN</t>
+  </si>
+  <si>
+    <t>wsouza43@gmail.com</t>
+  </si>
+  <si>
+    <t>1649203118</t>
+  </si>
+  <si>
+    <t>HAZEM ELARINY</t>
+  </si>
+  <si>
+    <t>helariny@gmail.com</t>
+  </si>
+  <si>
+    <t>1194778951</t>
+  </si>
+  <si>
+    <t>WILLIAM SLATER</t>
+  </si>
+  <si>
+    <t>lkslater@att.net</t>
+  </si>
+  <si>
+    <t>1871521898</t>
+  </si>
+  <si>
+    <t>ANNE RIZZO</t>
+  </si>
+  <si>
+    <t>fanf16@aol.com</t>
+  </si>
+  <si>
+    <t>1073735684</t>
+  </si>
+  <si>
+    <t>ELIZABETH MARSHALL</t>
+  </si>
+  <si>
+    <t>lizcmarshallmd@gmail.com</t>
+  </si>
+  <si>
+    <t>1326129545</t>
+  </si>
+  <si>
+    <t>DAVID STREET</t>
+  </si>
+  <si>
+    <t>linda@oregonsurgical.com</t>
+  </si>
+  <si>
+    <t>1508947730</t>
+  </si>
+  <si>
+    <t>WILLIAM FAUGHT</t>
+  </si>
+  <si>
+    <t>faughtmd@gmail.com</t>
+  </si>
+  <si>
+    <t>1356422596</t>
+  </si>
+  <si>
+    <t>DAVID TRAUL</t>
+  </si>
+  <si>
+    <t>dkttraul@hotmail.com</t>
+  </si>
+  <si>
+    <t>1144301300</t>
+  </si>
+  <si>
+    <t>MARK EATON</t>
+  </si>
+  <si>
+    <t>1609957877</t>
+  </si>
+  <si>
+    <t>JUAN CASTILLO</t>
+  </si>
+  <si>
+    <t>1710954680</t>
+  </si>
+  <si>
+    <t>VIRGINIA CHIANTELLA</t>
+  </si>
+  <si>
+    <t>vchiantellamd@gmail.com</t>
+  </si>
+  <si>
+    <t>1427083666</t>
+  </si>
+  <si>
+    <t>JAMES BALLARD</t>
+  </si>
+  <si>
+    <t>jamesballard@oregonvascular.org</t>
+  </si>
+  <si>
+    <t>1669474706</t>
+  </si>
+  <si>
+    <t>LUAT DUCKETT</t>
+  </si>
+  <si>
+    <t>infodedicatetosurgery@gmail.com</t>
+  </si>
+  <si>
+    <t>1578583308</t>
+  </si>
+  <si>
+    <t>DAVID PARKER</t>
+  </si>
+  <si>
+    <t>dparker@geisinger.edu</t>
+  </si>
+  <si>
+    <t>1285182949</t>
+  </si>
+  <si>
+    <t>KRISTINA LEMON</t>
+  </si>
+  <si>
+    <t>lemonkh@ucmail.uc.edu</t>
+  </si>
+  <si>
+    <t>1356338230</t>
+  </si>
+  <si>
+    <t>REGINA HAMPTON</t>
+  </si>
+  <si>
+    <t>rhampton@luminishealth.org</t>
+  </si>
+  <si>
+    <t>1053391227</t>
+  </si>
+  <si>
+    <t>ROBERT RICCA</t>
+  </si>
+  <si>
+    <t>robricca@yahoo.com</t>
+  </si>
+  <si>
+    <t>1356306658</t>
+  </si>
+  <si>
+    <t>MICHAEL TILLER</t>
+  </si>
+  <si>
+    <t>michael.m.tiller.mil@health.mil</t>
+  </si>
+  <si>
+    <t>1700964103</t>
+  </si>
+  <si>
+    <t>RODNEY CHAN</t>
+  </si>
+  <si>
+    <t>rodneykchan@gmail.com</t>
+  </si>
+  <si>
+    <t>1417272477</t>
+  </si>
+  <si>
+    <t>ERIC VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>ericvelazquezmd@gmail.com</t>
+  </si>
+  <si>
+    <t>1497833826</t>
+  </si>
+  <si>
+    <t>NASRIN ANSARI</t>
+  </si>
+  <si>
+    <t>nasrin.ansari@medstar.net</t>
+  </si>
+  <si>
+    <t>1700142593</t>
+  </si>
+  <si>
+    <t>NAVEEN KUMAR</t>
+  </si>
+  <si>
+    <t>DR.NAVEENGUPTA001@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>1306813480</t>
+  </si>
+  <si>
+    <t>RAFAEL SENERIZ ORTIZ</t>
+  </si>
+  <si>
+    <t>rafatt@hotmail.com</t>
+  </si>
+  <si>
+    <t>1841254422</t>
+  </si>
+  <si>
+    <t>HILLARY CHOLLET</t>
+  </si>
+  <si>
+    <t>hillary274@hotmail.com</t>
+  </si>
+  <si>
+    <t>1588774111</t>
+  </si>
+  <si>
+    <t>FERNANDO RIVERA CRUZ</t>
+  </si>
+  <si>
+    <t>info@cetlaspr.com</t>
+  </si>
+  <si>
+    <t>1720163397</t>
+  </si>
+  <si>
+    <t>ANGEL QUINONES RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>patricia.martinezquinones@duke.edu</t>
+  </si>
+  <si>
+    <t>1932202298</t>
+  </si>
+  <si>
+    <t>PETER KH GO</t>
+  </si>
+  <si>
+    <t>pgochee@gmail.com</t>
+  </si>
+  <si>
+    <t>1396925608</t>
+  </si>
+  <si>
+    <t>MELANY HUGHES</t>
+  </si>
+  <si>
+    <t>coppermallow@gmail.com</t>
+  </si>
+  <si>
+    <t>1639150246</t>
+  </si>
+  <si>
+    <t>CARLOS MARRERO ORTIZ</t>
+  </si>
+  <si>
+    <t>monchoperez1950@gmail.coms</t>
+  </si>
+  <si>
+    <t>1164538815</t>
+  </si>
+  <si>
+    <t>STEVEN FOWLER</t>
+  </si>
+  <si>
+    <t>fowlersf@ah.org</t>
+  </si>
+  <si>
+    <t>1972692929</t>
+  </si>
+  <si>
+    <t>JOSHUA PIERCE</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>1851496012</t>
+  </si>
+  <si>
+    <t>CHRISTOPHER JORDAN</t>
+  </si>
+  <si>
+    <t>cjordan@wilcoxhealth.org</t>
+  </si>
+  <si>
+    <t>1225256043</t>
+  </si>
+  <si>
+    <t>BENJAMIN PHILLIPS</t>
+  </si>
+  <si>
+    <t>drbenphillips@hotmail.com</t>
+  </si>
+  <si>
+    <t>1366460339</t>
+  </si>
+  <si>
+    <t>ALBERT WOO</t>
+  </si>
+  <si>
+    <t>albert_woo@brown.edu</t>
+  </si>
+  <si>
+    <t>1306047030</t>
+  </si>
+  <si>
+    <t>ANDREW EVANS</t>
+  </si>
+  <si>
+    <t>aevans@uoi.com</t>
+  </si>
+  <si>
+    <t>1760449920</t>
+  </si>
+  <si>
+    <t>PHILIP CHAIPIS</t>
+  </si>
+  <si>
+    <t>chaipis@hotmail.com</t>
+  </si>
+  <si>
+    <t>1073513032</t>
+  </si>
+  <si>
+    <t>CHARLES MORROW</t>
+  </si>
+  <si>
+    <t>cmorrow89@gmail.com</t>
+  </si>
+  <si>
+    <t>1013084441</t>
+  </si>
+  <si>
+    <t>ALFRED INES</t>
+  </si>
+  <si>
+    <t>inesa002@hawaii.rr.com</t>
+  </si>
+  <si>
+    <t>1245274497</t>
+  </si>
+  <si>
+    <t>MATTHEW METZ</t>
+  </si>
+  <si>
+    <t>matthew.metz@wvumedicine.org</t>
+  </si>
+  <si>
+    <t>1346289907</t>
+  </si>
+  <si>
+    <t>CHADWICK THOMAS</t>
+  </si>
+  <si>
+    <t>cvthomas71@gmail.com</t>
+  </si>
+  <si>
+    <t>1821059353</t>
+  </si>
+  <si>
+    <t>FREDRICK YOST</t>
+  </si>
+  <si>
+    <t>fyost@queens.org</t>
+  </si>
+  <si>
+    <t>1891738944</t>
+  </si>
+  <si>
+    <t>MIHAE YU</t>
+  </si>
+  <si>
+    <t>mihaey@hawaii.edu</t>
+  </si>
+  <si>
+    <t>1316011091</t>
+  </si>
+  <si>
+    <t>CASS NAKASONE</t>
+  </si>
+  <si>
+    <t>onohunter@icloud.com</t>
+  </si>
+  <si>
+    <t>1639231244</t>
+  </si>
+  <si>
+    <t>MICHAEL PASQUALE</t>
+  </si>
+  <si>
+    <t>michael.pasquale@jefferson.edu</t>
+  </si>
+  <si>
+    <t>1568474583</t>
+  </si>
+  <si>
+    <t>GLEN STRICKLAND</t>
+  </si>
+  <si>
+    <t>stricklandglen44@gmail.com</t>
+  </si>
+  <si>
+    <t>1467417188</t>
+  </si>
+  <si>
+    <t>KATHLEEN MAH</t>
+  </si>
+  <si>
+    <t>kathy_mah@hawaiiantel.net</t>
+  </si>
+  <si>
+    <t>1699782193</t>
+  </si>
+  <si>
+    <t>RICHARD FELTON</t>
+  </si>
+  <si>
+    <t>rjcf345@icloud.com</t>
+  </si>
+  <si>
+    <t>1295733905</t>
+  </si>
+  <si>
+    <t>MILES TOMMERAASEN</t>
+  </si>
+  <si>
+    <t>matommeraasen@gmail.com</t>
+  </si>
+  <si>
+    <t>1245241637</t>
+  </si>
+  <si>
+    <t>RONALD MYATICH</t>
+  </si>
+  <si>
+    <t>Myatich@aol.com</t>
+  </si>
+  <si>
+    <t>1598794364</t>
+  </si>
+  <si>
+    <t>EDWARD RAPP</t>
+  </si>
+  <si>
+    <t>erapp@premiersurgical.net</t>
+  </si>
+  <si>
+    <t>1831177377</t>
+  </si>
+  <si>
+    <t>HARRIS PARKER</t>
+  </si>
+  <si>
+    <t>samantha.floyd@prismahealth.org</t>
+  </si>
+  <si>
+    <t>1366429458</t>
+  </si>
+  <si>
+    <t>MICHAEL HOVEY</t>
+  </si>
+  <si>
+    <t>huntducks4@hotmail.com</t>
+  </si>
+  <si>
+    <t>1073764403</t>
+  </si>
+  <si>
+    <t>BERTRAND FONJI</t>
+  </si>
+  <si>
+    <t>bertfonji@gmail.com</t>
+  </si>
+  <si>
+    <t>1073569737</t>
+  </si>
+  <si>
+    <t>JOHN PENNINGS</t>
+  </si>
+  <si>
+    <t>john.pennings@nwsh.com</t>
+  </si>
+  <si>
+    <t>1679524805</t>
+  </si>
+  <si>
+    <t>THOMAS AMBROSE</t>
+  </si>
+  <si>
+    <t>thomas.ambrose@hshs.org</t>
+  </si>
+  <si>
+    <t>1356647051</t>
+  </si>
+  <si>
+    <t>KRISTIN FLOWERS</t>
+  </si>
+  <si>
+    <t>kristin.flowers@foundationhealth.org</t>
+  </si>
+  <si>
+    <t>1568443158</t>
+  </si>
+  <si>
+    <t>PAUL COLLINS</t>
+  </si>
+  <si>
+    <t>jade@baysurgicalspecialists.com</t>
+  </si>
+  <si>
+    <t>1427092444</t>
+  </si>
+  <si>
+    <t>DAVID DYER</t>
+  </si>
+  <si>
+    <t>davidsdyer@kcretina.com</t>
+  </si>
+  <si>
+    <t>1063598373</t>
+  </si>
+  <si>
+    <t>BERNARD BURGESS</t>
+  </si>
+  <si>
+    <t>BBurgess@hardinmedical.com</t>
+  </si>
+  <si>
+    <t>1750331757</t>
+  </si>
+  <si>
+    <t>ADAM DEUTCHMAN</t>
+  </si>
+  <si>
+    <t>a_deutchman@hotmail.com</t>
+  </si>
+  <si>
+    <t>1407850134</t>
+  </si>
+  <si>
+    <t>MICHAEL SARIDAKIS</t>
+  </si>
+  <si>
+    <t>asclepi@eplus.net</t>
+  </si>
+  <si>
+    <t>1225188501</t>
+  </si>
+  <si>
+    <t>JAMES MORRIS II</t>
+  </si>
+  <si>
+    <t>james.p.morris@kp.org</t>
+  </si>
+  <si>
+    <t>1497732929</t>
+  </si>
+  <si>
+    <t>SCOTT WATSON</t>
+  </si>
+  <si>
+    <t>scottwatson@centurylink.net</t>
+  </si>
+  <si>
+    <t>1962403378</t>
+  </si>
+  <si>
+    <t>NANCY BARRETT</t>
+  </si>
+  <si>
+    <t>barrettmd98@gmail.com</t>
+  </si>
+  <si>
+    <t>1447293675</t>
+  </si>
+  <si>
+    <t>TODD NICKLOES</t>
+  </si>
+  <si>
+    <t>tnickloe@utmck.edu</t>
+  </si>
+  <si>
+    <t>1245236983</t>
+  </si>
+  <si>
+    <t>JENNIFER MILLER</t>
+  </si>
+  <si>
+    <t>miller.jennifer.md@gmail.com</t>
+  </si>
+  <si>
+    <t>1073675492</t>
+  </si>
+  <si>
+    <t>MATTHEW BRIDGES</t>
+  </si>
+  <si>
+    <t>doctorbridges@gmail.com</t>
+  </si>
+  <si>
+    <t>1144205519</t>
+  </si>
+  <si>
+    <t>PAT WHITWORTH</t>
+  </si>
+  <si>
+    <t>Pat.whitworth@aptitudehealth.com</t>
+  </si>
+  <si>
+    <t>1588641187</t>
+  </si>
+  <si>
+    <t>MICHAEL HODGE</t>
+  </si>
+  <si>
+    <t>hodges@eyegroupsi.com</t>
+  </si>
+  <si>
+    <t>1194755454</t>
+  </si>
+  <si>
+    <t>MATTHEW MANCINI</t>
+  </si>
+  <si>
+    <t>mmancini@utmck.edu</t>
+  </si>
+  <si>
+    <t>1851528335</t>
+  </si>
+  <si>
+    <t>ERICH GERHARDT</t>
+  </si>
+  <si>
+    <t>Erich.gerhardt1@gmail.com</t>
+  </si>
+  <si>
+    <t>1437460854</t>
+  </si>
+  <si>
+    <t>JOHN HAGEDORN</t>
+  </si>
+  <si>
+    <t>Johnhagedorn@gmail.com</t>
+  </si>
+  <si>
+    <t>1093841728</t>
+  </si>
+  <si>
+    <t>DENNIS ROBISON</t>
+  </si>
+  <si>
+    <t>d.robison50@gmail.com</t>
+  </si>
+  <si>
+    <t>1790912228</t>
+  </si>
+  <si>
+    <t>TRAVIS HOLLOWAY</t>
+  </si>
+  <si>
+    <t>Travis.holloway2@hcahealthcare.com</t>
+  </si>
+  <si>
+    <t>1790076826</t>
+  </si>
+  <si>
+    <t>ELISABETH JONES BROWN</t>
+  </si>
+  <si>
+    <t>raeraegomez@gmail.com</t>
+  </si>
+  <si>
+    <t>1710274147</t>
+  </si>
+  <si>
+    <t>MICHAEL VAN HAL</t>
+  </si>
+  <si>
+    <t>vanvlietplasticsurgery@gmail.com</t>
+  </si>
+  <si>
+    <t>1811059264</t>
+  </si>
+  <si>
+    <t>BRYAN ANDERSON</t>
+  </si>
+  <si>
+    <t>bryanjkarena@gmail.com</t>
+  </si>
+  <si>
+    <t>1003060211</t>
+  </si>
+  <si>
+    <t>VICHIN PURI</t>
+  </si>
+  <si>
+    <t>vichinpuri@mhd.com</t>
+  </si>
+  <si>
+    <t>1700862786</t>
+  </si>
+  <si>
+    <t>ROBERT KORN</t>
+  </si>
+  <si>
+    <t>kornr@slhs.org</t>
+  </si>
+  <si>
+    <t>1083684203</t>
+  </si>
+  <si>
+    <t>MICHAEL MAY</t>
+  </si>
+  <si>
+    <t>mpmays01@gmail.com</t>
+  </si>
+  <si>
+    <t>1184652364</t>
+  </si>
+  <si>
+    <t>DAVID BROWN</t>
+  </si>
+  <si>
+    <t>Drdavidlbrown@gmail.com</t>
+  </si>
+  <si>
+    <t>1366465197</t>
+  </si>
+  <si>
+    <t>DAVID CHAMBERLAIN</t>
+  </si>
+  <si>
+    <t>chamberlain_2@msn.com</t>
+  </si>
+  <si>
+    <t>1639279698</t>
+  </si>
+  <si>
+    <t>JOHN MILLER</t>
+  </si>
+  <si>
+    <t>Braintruster@gmail.com</t>
+  </si>
+  <si>
+    <t>1376565473</t>
+  </si>
+  <si>
+    <t>ERIC BAIRD</t>
+  </si>
+  <si>
+    <t>eric.baird88@gmail.com</t>
+  </si>
+  <si>
+    <t>1477593648</t>
+  </si>
+  <si>
+    <t>RYAN HARDY</t>
+  </si>
+  <si>
+    <t>rhardy@icom.edu</t>
+  </si>
+  <si>
+    <t>1679622542</t>
+  </si>
+  <si>
+    <t>ELLEN REYNOLDS</t>
+  </si>
+  <si>
+    <t>reynoldsellenm@gmail.com</t>
+  </si>
+  <si>
+    <t>1548423213</t>
+  </si>
+  <si>
+    <t>LEVI PROCTER</t>
+  </si>
+  <si>
+    <t>levidprocter@gmail.com</t>
+  </si>
+  <si>
+    <t>1730355447</t>
+  </si>
+  <si>
+    <t>MICHAEL O'REILLY</t>
+  </si>
+  <si>
+    <t>rtedesco1@northwell.edu</t>
+  </si>
+  <si>
+    <t>1295928992</t>
+  </si>
+  <si>
+    <t>DUANE DUKE</t>
+  </si>
+  <si>
+    <t>duane.duke@nemours.org</t>
+  </si>
+  <si>
+    <t>1760578439</t>
+  </si>
+  <si>
+    <t>EDGAR RODAS</t>
+  </si>
+  <si>
+    <t>ebrodas@gmail.com</t>
+  </si>
+  <si>
+    <t>1780900498</t>
+  </si>
+  <si>
+    <t>ANTHONY HO</t>
+  </si>
+  <si>
+    <t>holdenanthony311@gmail.com</t>
+  </si>
+  <si>
+    <t>1376694927</t>
+  </si>
+  <si>
+    <t>MICHAEL DAVOREN</t>
+  </si>
+  <si>
+    <t>michaeldavorenmd@gmail.com</t>
+  </si>
+  <si>
+    <t>1780611178</t>
+  </si>
+  <si>
+    <t>KENTON SCHOONOVER</t>
+  </si>
+  <si>
+    <t>kenton@kansasplasticsurgery.com</t>
+  </si>
+  <si>
+    <t>1326045113</t>
+  </si>
+  <si>
+    <t>RONALD NOLD</t>
+  </si>
+  <si>
+    <t>jnoldscarmaker@gmail.com</t>
+  </si>
+  <si>
+    <t>1679663959</t>
+  </si>
+  <si>
+    <t>GLENDA WRENSFORD</t>
+  </si>
+  <si>
+    <t>gwrens1@hotmail.com</t>
+  </si>
+  <si>
+    <t>1811979271</t>
+  </si>
+  <si>
+    <t>MARK WHITAKER</t>
+  </si>
+  <si>
+    <t>mwhitaker1993@gmail.com</t>
+  </si>
+  <si>
+    <t>1548266893</t>
+  </si>
+  <si>
+    <t>SIMON DREW</t>
+  </si>
+  <si>
+    <t>sdrew6583@gmail.com</t>
+  </si>
+  <si>
+    <t>1760477533</t>
+  </si>
+  <si>
+    <t>CHRISTOPHER HULTS</t>
+  </si>
+  <si>
+    <t>cmhults@gmail.com</t>
+  </si>
+  <si>
+    <t>1073839122</t>
+  </si>
+  <si>
+    <t>TIMOTHY FELDMANN</t>
+  </si>
+  <si>
+    <t>tim.feldmann@alumni.nd.edu</t>
+  </si>
+  <si>
+    <t>1780846592</t>
+  </si>
+  <si>
+    <t>JOSHUA JUDGE</t>
+  </si>
+  <si>
+    <t>jmjudg82@gmail.com</t>
+  </si>
+  <si>
+    <t>1851549455</t>
+  </si>
+  <si>
+    <t>CHAD SMITH</t>
+  </si>
+  <si>
+    <t>jessica.tardd@orlandohealth.com</t>
+  </si>
+  <si>
+    <t>1205064565</t>
+  </si>
+  <si>
+    <t>REBECCA FREEMAN</t>
+  </si>
+  <si>
+    <t>jenniferb@olympiasurgery.com</t>
+  </si>
+  <si>
+    <t>1528070067</t>
+  </si>
+  <si>
+    <t>DHAVAL ADHVARYU</t>
+  </si>
+  <si>
+    <t>dha439@brgeneral.org</t>
+  </si>
+  <si>
+    <t>1831159631</t>
+  </si>
+  <si>
+    <t>CLARK WARDEN</t>
+  </si>
+  <si>
+    <t>Clark.Warden@fmolhs.org</t>
+  </si>
+  <si>
+    <t>1821040528</t>
+  </si>
+  <si>
+    <t>THERESA QUINN</t>
+  </si>
+  <si>
+    <t>paulsen6@me.com</t>
+  </si>
+  <si>
+    <t>1437168473</t>
+  </si>
+  <si>
+    <t>THEODORE PARINS</t>
+  </si>
+  <si>
+    <t>ParinsMD@iCloud.com</t>
+  </si>
+  <si>
+    <t>1366449290</t>
+  </si>
+  <si>
+    <t>PHILIP GACHASSIN</t>
+  </si>
+  <si>
+    <t>philip.gachassin@ochsner.org</t>
+  </si>
+  <si>
+    <t>1821007022</t>
+  </si>
+  <si>
+    <t>KEVIN O'HALLORAN</t>
+  </si>
+  <si>
+    <t>gallokm@upmc.edu</t>
+  </si>
+  <si>
+    <t>1427074509</t>
+  </si>
+  <si>
+    <t>JONATHAN MCLAUGHLIN</t>
+  </si>
+  <si>
+    <t>mclaughlin.jonathang@gmail.com</t>
+  </si>
+  <si>
+    <t>1366436891</t>
+  </si>
+  <si>
+    <t>MICHAEL HOLLAND</t>
+  </si>
+  <si>
+    <t>mikehollands.au@gmail.com</t>
+  </si>
+  <si>
+    <t>1538259478</t>
+  </si>
+  <si>
+    <t>JAMES BENNETT</t>
+  </si>
+  <si>
+    <t>doctors@midtown-urology.com</t>
+  </si>
+  <si>
+    <t>1740209519</t>
+  </si>
+  <si>
+    <t>JOHN WARD</t>
+  </si>
+  <si>
+    <t>johnfward@me.com</t>
+  </si>
+  <si>
+    <t>1427054022</t>
+  </si>
+  <si>
+    <t>LARRY SASAKI</t>
+  </si>
+  <si>
+    <t>larrysasaki@gmail.com</t>
+  </si>
+  <si>
+    <t>1184912719</t>
+  </si>
+  <si>
+    <t>MICHAEL ST. ONGE</t>
+  </si>
+  <si>
+    <t>mstjean.msj@gmail.com</t>
+  </si>
+  <si>
+    <t>1912227083</t>
+  </si>
+  <si>
+    <t>NOVA SZOKA</t>
+  </si>
+  <si>
+    <t>novaszoka@gmail.com</t>
+  </si>
+  <si>
+    <t>1215027883</t>
+  </si>
+  <si>
+    <t>RICHARD JACKSON</t>
+  </si>
+  <si>
+    <t>JacksonRichardJ@uams.edu</t>
+  </si>
+  <si>
+    <t>1649296237</t>
+  </si>
+  <si>
+    <t>JUAN SANABRIA</t>
+  </si>
+  <si>
+    <t>juan.sanabria0430@gmail.com</t>
+  </si>
+  <si>
+    <t>1447252085</t>
+  </si>
+  <si>
+    <t>1902049273</t>
+  </si>
+  <si>
+    <t>BRENESSA LINDEMAN</t>
+  </si>
+  <si>
+    <t>blindeman@uabmc.edu</t>
+  </si>
+  <si>
+    <t>1083637920</t>
+  </si>
+  <si>
+    <t>ANTHONY QUINN</t>
+  </si>
+  <si>
+    <t>ctquinn@aol.com</t>
+  </si>
+  <si>
+    <t>1942428784</t>
+  </si>
+  <si>
+    <t>YEE LEE CHEAH</t>
+  </si>
+  <si>
+    <t>kjcastro@houstonmethodist.org</t>
+  </si>
+  <si>
+    <t>1780620062</t>
+  </si>
+  <si>
+    <t>MICHAEL MAROHN</t>
+  </si>
+  <si>
+    <t>mrmarohn@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -391,11 +3052,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C299"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.77734375" customWidth="1"/>
-    <col min="2" max="2" width="35.88671875" customWidth="1"/>
+    <col min="1" max="1" width="21.5546875" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="27.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -409,6 +3071,3284 @@
         <v>2</v>
       </c>
     </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>63</v>
+      </c>
+      <c r="B22" t="s">
+        <v>64</v>
+      </c>
+      <c r="C22" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>66</v>
+      </c>
+      <c r="B23" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>69</v>
+      </c>
+      <c r="B24" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>72</v>
+      </c>
+      <c r="B25" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>75</v>
+      </c>
+      <c r="B26" t="s">
+        <v>76</v>
+      </c>
+      <c r="C26" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>78</v>
+      </c>
+      <c r="B27" t="s">
+        <v>79</v>
+      </c>
+      <c r="C27" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28" t="s">
+        <v>82</v>
+      </c>
+      <c r="C28" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>84</v>
+      </c>
+      <c r="B29" t="s">
+        <v>85</v>
+      </c>
+      <c r="C29" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>87</v>
+      </c>
+      <c r="B30" t="s">
+        <v>88</v>
+      </c>
+      <c r="C30" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>90</v>
+      </c>
+      <c r="B31" t="s">
+        <v>91</v>
+      </c>
+      <c r="C31" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>93</v>
+      </c>
+      <c r="B32" t="s">
+        <v>94</v>
+      </c>
+      <c r="C32" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>96</v>
+      </c>
+      <c r="B33" t="s">
+        <v>97</v>
+      </c>
+      <c r="C33" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>99</v>
+      </c>
+      <c r="B34" t="s">
+        <v>100</v>
+      </c>
+      <c r="C34" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>102</v>
+      </c>
+      <c r="B35" t="s">
+        <v>103</v>
+      </c>
+      <c r="C35" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>105</v>
+      </c>
+      <c r="B36" t="s">
+        <v>106</v>
+      </c>
+      <c r="C36" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>108</v>
+      </c>
+      <c r="B37" t="s">
+        <v>109</v>
+      </c>
+      <c r="C37" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>111</v>
+      </c>
+      <c r="B38" t="s">
+        <v>112</v>
+      </c>
+      <c r="C38" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>114</v>
+      </c>
+      <c r="B39" t="s">
+        <v>115</v>
+      </c>
+      <c r="C39" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>117</v>
+      </c>
+      <c r="B40" t="s">
+        <v>118</v>
+      </c>
+      <c r="C40" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>120</v>
+      </c>
+      <c r="B41" t="s">
+        <v>121</v>
+      </c>
+      <c r="C41" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>123</v>
+      </c>
+      <c r="B42" t="s">
+        <v>124</v>
+      </c>
+      <c r="C42" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>126</v>
+      </c>
+      <c r="B43" t="s">
+        <v>127</v>
+      </c>
+      <c r="C43" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>129</v>
+      </c>
+      <c r="B44" t="s">
+        <v>130</v>
+      </c>
+      <c r="C44" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>132</v>
+      </c>
+      <c r="B45" t="s">
+        <v>133</v>
+      </c>
+      <c r="C45" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>135</v>
+      </c>
+      <c r="B46" t="s">
+        <v>136</v>
+      </c>
+      <c r="C46" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>138</v>
+      </c>
+      <c r="B47" t="s">
+        <v>139</v>
+      </c>
+      <c r="C47" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>141</v>
+      </c>
+      <c r="B48" t="s">
+        <v>142</v>
+      </c>
+      <c r="C48" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>144</v>
+      </c>
+      <c r="B49" t="s">
+        <v>145</v>
+      </c>
+      <c r="C49" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>147</v>
+      </c>
+      <c r="B50" t="s">
+        <v>148</v>
+      </c>
+      <c r="C50" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>150</v>
+      </c>
+      <c r="B51" t="s">
+        <v>151</v>
+      </c>
+      <c r="C51" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>153</v>
+      </c>
+      <c r="B52" t="s">
+        <v>154</v>
+      </c>
+      <c r="C52" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>156</v>
+      </c>
+      <c r="B53" t="s">
+        <v>157</v>
+      </c>
+      <c r="C53" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>159</v>
+      </c>
+      <c r="B54" t="s">
+        <v>160</v>
+      </c>
+      <c r="C54" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>162</v>
+      </c>
+      <c r="B55" t="s">
+        <v>163</v>
+      </c>
+      <c r="C55" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>165</v>
+      </c>
+      <c r="B56" t="s">
+        <v>166</v>
+      </c>
+      <c r="C56" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>168</v>
+      </c>
+      <c r="B57" t="s">
+        <v>169</v>
+      </c>
+      <c r="C57" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>171</v>
+      </c>
+      <c r="B58" t="s">
+        <v>172</v>
+      </c>
+      <c r="C58" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>174</v>
+      </c>
+      <c r="B59" t="s">
+        <v>175</v>
+      </c>
+      <c r="C59" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>177</v>
+      </c>
+      <c r="B60" t="s">
+        <v>178</v>
+      </c>
+      <c r="C60" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>180</v>
+      </c>
+      <c r="B61" t="s">
+        <v>181</v>
+      </c>
+      <c r="C61" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>183</v>
+      </c>
+      <c r="B62" t="s">
+        <v>184</v>
+      </c>
+      <c r="C62" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>186</v>
+      </c>
+      <c r="B63" t="s">
+        <v>187</v>
+      </c>
+      <c r="C63" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>189</v>
+      </c>
+      <c r="B64" t="s">
+        <v>190</v>
+      </c>
+      <c r="C64" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>192</v>
+      </c>
+      <c r="B65" t="s">
+        <v>193</v>
+      </c>
+      <c r="C65" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>195</v>
+      </c>
+      <c r="B66" t="s">
+        <v>196</v>
+      </c>
+      <c r="C66" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>198</v>
+      </c>
+      <c r="B67" t="s">
+        <v>199</v>
+      </c>
+      <c r="C67" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>201</v>
+      </c>
+      <c r="B68" t="s">
+        <v>202</v>
+      </c>
+      <c r="C68" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>204</v>
+      </c>
+      <c r="B69" t="s">
+        <v>205</v>
+      </c>
+      <c r="C69" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>207</v>
+      </c>
+      <c r="B70" t="s">
+        <v>208</v>
+      </c>
+      <c r="C70" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>210</v>
+      </c>
+      <c r="B71" t="s">
+        <v>211</v>
+      </c>
+      <c r="C71" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>213</v>
+      </c>
+      <c r="B72" t="s">
+        <v>214</v>
+      </c>
+      <c r="C72" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>216</v>
+      </c>
+      <c r="B73" t="s">
+        <v>217</v>
+      </c>
+      <c r="C73" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>219</v>
+      </c>
+      <c r="B74" t="s">
+        <v>220</v>
+      </c>
+      <c r="C74" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>222</v>
+      </c>
+      <c r="B75" t="s">
+        <v>223</v>
+      </c>
+      <c r="C75" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>225</v>
+      </c>
+      <c r="B76" t="s">
+        <v>226</v>
+      </c>
+      <c r="C76" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>228</v>
+      </c>
+      <c r="B77" t="s">
+        <v>229</v>
+      </c>
+      <c r="C77" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>231</v>
+      </c>
+      <c r="B78" t="s">
+        <v>232</v>
+      </c>
+      <c r="C78" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>234</v>
+      </c>
+      <c r="B79" t="s">
+        <v>235</v>
+      </c>
+      <c r="C79" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>237</v>
+      </c>
+      <c r="B80" t="s">
+        <v>238</v>
+      </c>
+      <c r="C80" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>240</v>
+      </c>
+      <c r="B81" t="s">
+        <v>241</v>
+      </c>
+      <c r="C81" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>243</v>
+      </c>
+      <c r="B82" t="s">
+        <v>244</v>
+      </c>
+      <c r="C82" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>246</v>
+      </c>
+      <c r="B83" t="s">
+        <v>247</v>
+      </c>
+      <c r="C83" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>249</v>
+      </c>
+      <c r="B84" t="s">
+        <v>250</v>
+      </c>
+      <c r="C84" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>252</v>
+      </c>
+      <c r="B85" t="s">
+        <v>253</v>
+      </c>
+      <c r="C85" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>255</v>
+      </c>
+      <c r="B86" t="s">
+        <v>256</v>
+      </c>
+      <c r="C86" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>258</v>
+      </c>
+      <c r="B87" t="s">
+        <v>259</v>
+      </c>
+      <c r="C87" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>261</v>
+      </c>
+      <c r="B88" t="s">
+        <v>262</v>
+      </c>
+      <c r="C88" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>264</v>
+      </c>
+      <c r="B89" t="s">
+        <v>265</v>
+      </c>
+      <c r="C89" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>267</v>
+      </c>
+      <c r="B90" t="s">
+        <v>268</v>
+      </c>
+      <c r="C90" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>270</v>
+      </c>
+      <c r="B91" t="s">
+        <v>271</v>
+      </c>
+      <c r="C91" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>273</v>
+      </c>
+      <c r="B92" t="s">
+        <v>274</v>
+      </c>
+      <c r="C92" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>276</v>
+      </c>
+      <c r="B93" t="s">
+        <v>277</v>
+      </c>
+      <c r="C93" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>279</v>
+      </c>
+      <c r="B94" t="s">
+        <v>280</v>
+      </c>
+      <c r="C94" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>282</v>
+      </c>
+      <c r="B95" t="s">
+        <v>283</v>
+      </c>
+      <c r="C95" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>285</v>
+      </c>
+      <c r="B96" t="s">
+        <v>286</v>
+      </c>
+      <c r="C96" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>288</v>
+      </c>
+      <c r="B97" t="s">
+        <v>289</v>
+      </c>
+      <c r="C97" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>291</v>
+      </c>
+      <c r="B98" t="s">
+        <v>292</v>
+      </c>
+      <c r="C98" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>294</v>
+      </c>
+      <c r="B99" t="s">
+        <v>295</v>
+      </c>
+      <c r="C99" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>297</v>
+      </c>
+      <c r="B100" t="s">
+        <v>298</v>
+      </c>
+      <c r="C100" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>300</v>
+      </c>
+      <c r="B101" t="s">
+        <v>301</v>
+      </c>
+      <c r="C101" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>303</v>
+      </c>
+      <c r="B102" t="s">
+        <v>304</v>
+      </c>
+      <c r="C102" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>306</v>
+      </c>
+      <c r="B103" t="s">
+        <v>307</v>
+      </c>
+      <c r="C103" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>309</v>
+      </c>
+      <c r="B104" t="s">
+        <v>310</v>
+      </c>
+      <c r="C104" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>312</v>
+      </c>
+      <c r="B105" t="s">
+        <v>313</v>
+      </c>
+      <c r="C105" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>315</v>
+      </c>
+      <c r="B106" t="s">
+        <v>316</v>
+      </c>
+      <c r="C106" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>318</v>
+      </c>
+      <c r="B107" t="s">
+        <v>319</v>
+      </c>
+      <c r="C107" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>321</v>
+      </c>
+      <c r="B108" t="s">
+        <v>322</v>
+      </c>
+      <c r="C108" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>324</v>
+      </c>
+      <c r="B109" t="s">
+        <v>325</v>
+      </c>
+      <c r="C109" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>327</v>
+      </c>
+      <c r="B110" t="s">
+        <v>328</v>
+      </c>
+      <c r="C110" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>330</v>
+      </c>
+      <c r="B111" t="s">
+        <v>331</v>
+      </c>
+      <c r="C111" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>333</v>
+      </c>
+      <c r="B112" t="s">
+        <v>334</v>
+      </c>
+      <c r="C112" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>336</v>
+      </c>
+      <c r="B113" t="s">
+        <v>337</v>
+      </c>
+      <c r="C113" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>339</v>
+      </c>
+      <c r="B114" t="s">
+        <v>340</v>
+      </c>
+      <c r="C114" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>342</v>
+      </c>
+      <c r="B115" t="s">
+        <v>343</v>
+      </c>
+      <c r="C115" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>345</v>
+      </c>
+      <c r="B116" t="s">
+        <v>346</v>
+      </c>
+      <c r="C116" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>348</v>
+      </c>
+      <c r="B117" t="s">
+        <v>349</v>
+      </c>
+      <c r="C117" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>351</v>
+      </c>
+      <c r="B118" t="s">
+        <v>352</v>
+      </c>
+      <c r="C118" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>354</v>
+      </c>
+      <c r="B119" t="s">
+        <v>355</v>
+      </c>
+      <c r="C119" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>357</v>
+      </c>
+      <c r="B120" t="s">
+        <v>358</v>
+      </c>
+      <c r="C120" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>360</v>
+      </c>
+      <c r="B121" t="s">
+        <v>361</v>
+      </c>
+      <c r="C121" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>363</v>
+      </c>
+      <c r="B122" t="s">
+        <v>364</v>
+      </c>
+      <c r="C122" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>366</v>
+      </c>
+      <c r="B123" t="s">
+        <v>367</v>
+      </c>
+      <c r="C123" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>369</v>
+      </c>
+      <c r="B124" t="s">
+        <v>370</v>
+      </c>
+      <c r="C124" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>372</v>
+      </c>
+      <c r="B125" t="s">
+        <v>373</v>
+      </c>
+      <c r="C125" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>375</v>
+      </c>
+      <c r="B126" t="s">
+        <v>376</v>
+      </c>
+      <c r="C126" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>378</v>
+      </c>
+      <c r="B127" t="s">
+        <v>379</v>
+      </c>
+      <c r="C127" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>381</v>
+      </c>
+      <c r="B128" t="s">
+        <v>382</v>
+      </c>
+      <c r="C128" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>384</v>
+      </c>
+      <c r="B129" t="s">
+        <v>385</v>
+      </c>
+      <c r="C129" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>387</v>
+      </c>
+      <c r="B130" t="s">
+        <v>388</v>
+      </c>
+      <c r="C130" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>390</v>
+      </c>
+      <c r="B131" t="s">
+        <v>391</v>
+      </c>
+      <c r="C131" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>393</v>
+      </c>
+      <c r="B132" t="s">
+        <v>394</v>
+      </c>
+      <c r="C132" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>396</v>
+      </c>
+      <c r="B133" t="s">
+        <v>397</v>
+      </c>
+      <c r="C133" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>399</v>
+      </c>
+      <c r="B134" t="s">
+        <v>400</v>
+      </c>
+      <c r="C134" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>402</v>
+      </c>
+      <c r="B135" t="s">
+        <v>403</v>
+      </c>
+      <c r="C135" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>404</v>
+      </c>
+      <c r="B136" t="s">
+        <v>405</v>
+      </c>
+      <c r="C136" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>407</v>
+      </c>
+      <c r="B137" t="s">
+        <v>408</v>
+      </c>
+      <c r="C137" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>410</v>
+      </c>
+      <c r="B138" t="s">
+        <v>411</v>
+      </c>
+      <c r="C138" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>413</v>
+      </c>
+      <c r="B139" t="s">
+        <v>414</v>
+      </c>
+      <c r="C139" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>416</v>
+      </c>
+      <c r="B140" t="s">
+        <v>417</v>
+      </c>
+      <c r="C140" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>419</v>
+      </c>
+      <c r="B141" t="s">
+        <v>420</v>
+      </c>
+      <c r="C141" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>422</v>
+      </c>
+      <c r="B142" t="s">
+        <v>423</v>
+      </c>
+      <c r="C142" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>425</v>
+      </c>
+      <c r="B143" t="s">
+        <v>426</v>
+      </c>
+      <c r="C143" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>428</v>
+      </c>
+      <c r="B144" t="s">
+        <v>429</v>
+      </c>
+      <c r="C144" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>431</v>
+      </c>
+      <c r="B145" t="s">
+        <v>432</v>
+      </c>
+      <c r="C145" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>434</v>
+      </c>
+      <c r="B146" t="s">
+        <v>435</v>
+      </c>
+      <c r="C146" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>437</v>
+      </c>
+      <c r="B147" t="s">
+        <v>438</v>
+      </c>
+      <c r="C147" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>440</v>
+      </c>
+      <c r="B148" t="s">
+        <v>441</v>
+      </c>
+      <c r="C148" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>443</v>
+      </c>
+      <c r="B149" t="s">
+        <v>444</v>
+      </c>
+      <c r="C149" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>446</v>
+      </c>
+      <c r="B150" t="s">
+        <v>447</v>
+      </c>
+      <c r="C150" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>449</v>
+      </c>
+      <c r="B151" t="s">
+        <v>450</v>
+      </c>
+      <c r="C151" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>452</v>
+      </c>
+      <c r="B152" t="s">
+        <v>453</v>
+      </c>
+      <c r="C152" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>455</v>
+      </c>
+      <c r="B153" t="s">
+        <v>456</v>
+      </c>
+      <c r="C153" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>458</v>
+      </c>
+      <c r="B154" t="s">
+        <v>459</v>
+      </c>
+      <c r="C154" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>461</v>
+      </c>
+      <c r="B155" t="s">
+        <v>462</v>
+      </c>
+      <c r="C155" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>464</v>
+      </c>
+      <c r="B156" t="s">
+        <v>465</v>
+      </c>
+      <c r="C156" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>467</v>
+      </c>
+      <c r="B157" t="s">
+        <v>468</v>
+      </c>
+      <c r="C157" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>470</v>
+      </c>
+      <c r="B158" t="s">
+        <v>471</v>
+      </c>
+      <c r="C158" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>473</v>
+      </c>
+      <c r="B159" t="s">
+        <v>474</v>
+      </c>
+      <c r="C159" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>476</v>
+      </c>
+      <c r="B160" t="s">
+        <v>477</v>
+      </c>
+      <c r="C160" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>479</v>
+      </c>
+      <c r="B161" t="s">
+        <v>480</v>
+      </c>
+      <c r="C161" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>482</v>
+      </c>
+      <c r="B162" t="s">
+        <v>262</v>
+      </c>
+      <c r="C162" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>483</v>
+      </c>
+      <c r="B163" t="s">
+        <v>484</v>
+      </c>
+      <c r="C163" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>486</v>
+      </c>
+      <c r="B164" t="s">
+        <v>487</v>
+      </c>
+      <c r="C164" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>489</v>
+      </c>
+      <c r="B165" t="s">
+        <v>490</v>
+      </c>
+      <c r="C165" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>492</v>
+      </c>
+      <c r="B166" t="s">
+        <v>493</v>
+      </c>
+      <c r="C166" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>495</v>
+      </c>
+      <c r="B167" t="s">
+        <v>496</v>
+      </c>
+      <c r="C167" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>498</v>
+      </c>
+      <c r="B168" t="s">
+        <v>499</v>
+      </c>
+      <c r="C168" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>501</v>
+      </c>
+      <c r="B169" t="s">
+        <v>502</v>
+      </c>
+      <c r="C169" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>504</v>
+      </c>
+      <c r="B170" t="s">
+        <v>505</v>
+      </c>
+      <c r="C170" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>507</v>
+      </c>
+      <c r="B171" t="s">
+        <v>508</v>
+      </c>
+      <c r="C171" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>510</v>
+      </c>
+      <c r="B172" t="s">
+        <v>511</v>
+      </c>
+      <c r="C172" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>513</v>
+      </c>
+      <c r="B173" t="s">
+        <v>514</v>
+      </c>
+      <c r="C173" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>516</v>
+      </c>
+      <c r="B174" t="s">
+        <v>517</v>
+      </c>
+      <c r="C174" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>519</v>
+      </c>
+      <c r="B175" t="s">
+        <v>520</v>
+      </c>
+      <c r="C175" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>522</v>
+      </c>
+      <c r="B176" t="s">
+        <v>523</v>
+      </c>
+      <c r="C176" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>525</v>
+      </c>
+      <c r="B177" t="s">
+        <v>526</v>
+      </c>
+      <c r="C177" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>528</v>
+      </c>
+      <c r="B178" t="s">
+        <v>529</v>
+      </c>
+      <c r="C178" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>531</v>
+      </c>
+      <c r="B179" t="s">
+        <v>532</v>
+      </c>
+      <c r="C179" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>534</v>
+      </c>
+      <c r="B180" t="s">
+        <v>535</v>
+      </c>
+      <c r="C180" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>537</v>
+      </c>
+      <c r="B181" t="s">
+        <v>538</v>
+      </c>
+      <c r="C181" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>540</v>
+      </c>
+      <c r="B182" t="s">
+        <v>541</v>
+      </c>
+      <c r="C182" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
+        <v>543</v>
+      </c>
+      <c r="B183" t="s">
+        <v>544</v>
+      </c>
+      <c r="C183" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>546</v>
+      </c>
+      <c r="B184" t="s">
+        <v>547</v>
+      </c>
+      <c r="C184" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
+        <v>549</v>
+      </c>
+      <c r="B185" t="s">
+        <v>550</v>
+      </c>
+      <c r="C185" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>552</v>
+      </c>
+      <c r="B186" t="s">
+        <v>553</v>
+      </c>
+      <c r="C186" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>554</v>
+      </c>
+      <c r="B187" t="s">
+        <v>555</v>
+      </c>
+      <c r="C187" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>556</v>
+      </c>
+      <c r="B188" t="s">
+        <v>557</v>
+      </c>
+      <c r="C188" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>559</v>
+      </c>
+      <c r="B189" t="s">
+        <v>560</v>
+      </c>
+      <c r="C189" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>562</v>
+      </c>
+      <c r="B190" t="s">
+        <v>563</v>
+      </c>
+      <c r="C190" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>565</v>
+      </c>
+      <c r="B191" t="s">
+        <v>566</v>
+      </c>
+      <c r="C191" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
+        <v>568</v>
+      </c>
+      <c r="B192" t="s">
+        <v>569</v>
+      </c>
+      <c r="C192" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
+        <v>571</v>
+      </c>
+      <c r="B193" t="s">
+        <v>572</v>
+      </c>
+      <c r="C193" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
+        <v>574</v>
+      </c>
+      <c r="B194" t="s">
+        <v>575</v>
+      </c>
+      <c r="C194" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
+        <v>577</v>
+      </c>
+      <c r="B195" t="s">
+        <v>578</v>
+      </c>
+      <c r="C195" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
+        <v>580</v>
+      </c>
+      <c r="B196" t="s">
+        <v>581</v>
+      </c>
+      <c r="C196" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
+        <v>583</v>
+      </c>
+      <c r="B197" t="s">
+        <v>584</v>
+      </c>
+      <c r="C197" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
+        <v>586</v>
+      </c>
+      <c r="B198" t="s">
+        <v>587</v>
+      </c>
+      <c r="C198" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
+        <v>589</v>
+      </c>
+      <c r="B199" t="s">
+        <v>590</v>
+      </c>
+      <c r="C199" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
+        <v>592</v>
+      </c>
+      <c r="B200" t="s">
+        <v>593</v>
+      </c>
+      <c r="C200" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
+        <v>595</v>
+      </c>
+      <c r="B201" t="s">
+        <v>596</v>
+      </c>
+      <c r="C201" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A202" t="s">
+        <v>598</v>
+      </c>
+      <c r="B202" t="s">
+        <v>599</v>
+      </c>
+      <c r="C202" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A203" t="s">
+        <v>601</v>
+      </c>
+      <c r="B203" t="s">
+        <v>602</v>
+      </c>
+      <c r="C203" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A204" t="s">
+        <v>604</v>
+      </c>
+      <c r="B204" t="s">
+        <v>605</v>
+      </c>
+      <c r="C204" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A205" t="s">
+        <v>607</v>
+      </c>
+      <c r="B205" t="s">
+        <v>608</v>
+      </c>
+      <c r="C205" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A206" t="s">
+        <v>610</v>
+      </c>
+      <c r="B206" t="s">
+        <v>611</v>
+      </c>
+      <c r="C206" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A207" t="s">
+        <v>613</v>
+      </c>
+      <c r="B207" t="s">
+        <v>614</v>
+      </c>
+      <c r="C207" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A208" t="s">
+        <v>616</v>
+      </c>
+      <c r="B208" t="s">
+        <v>617</v>
+      </c>
+      <c r="C208" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A209" t="s">
+        <v>619</v>
+      </c>
+      <c r="B209" t="s">
+        <v>620</v>
+      </c>
+      <c r="C209" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A210" t="s">
+        <v>622</v>
+      </c>
+      <c r="B210" t="s">
+        <v>623</v>
+      </c>
+      <c r="C210" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A211" t="s">
+        <v>625</v>
+      </c>
+      <c r="B211" t="s">
+        <v>626</v>
+      </c>
+      <c r="C211" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A212" t="s">
+        <v>628</v>
+      </c>
+      <c r="B212" t="s">
+        <v>629</v>
+      </c>
+      <c r="C212" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A213" t="s">
+        <v>631</v>
+      </c>
+      <c r="B213" t="s">
+        <v>632</v>
+      </c>
+      <c r="C213" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A214" t="s">
+        <v>634</v>
+      </c>
+      <c r="B214" t="s">
+        <v>635</v>
+      </c>
+      <c r="C214" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A215" t="s">
+        <v>637</v>
+      </c>
+      <c r="B215" t="s">
+        <v>638</v>
+      </c>
+      <c r="C215" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A216" t="s">
+        <v>640</v>
+      </c>
+      <c r="B216" t="s">
+        <v>641</v>
+      </c>
+      <c r="C216" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A217" t="s">
+        <v>643</v>
+      </c>
+      <c r="B217" t="s">
+        <v>644</v>
+      </c>
+      <c r="C217" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A218" t="s">
+        <v>646</v>
+      </c>
+      <c r="B218" t="s">
+        <v>647</v>
+      </c>
+      <c r="C218" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A219" t="s">
+        <v>649</v>
+      </c>
+      <c r="B219" t="s">
+        <v>650</v>
+      </c>
+      <c r="C219" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A220" t="s">
+        <v>652</v>
+      </c>
+      <c r="B220" t="s">
+        <v>653</v>
+      </c>
+      <c r="C220" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A221" t="s">
+        <v>655</v>
+      </c>
+      <c r="B221" t="s">
+        <v>656</v>
+      </c>
+      <c r="C221" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A222" t="s">
+        <v>658</v>
+      </c>
+      <c r="B222" t="s">
+        <v>659</v>
+      </c>
+      <c r="C222" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A223" t="s">
+        <v>661</v>
+      </c>
+      <c r="B223" t="s">
+        <v>662</v>
+      </c>
+      <c r="C223" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A224" t="s">
+        <v>664</v>
+      </c>
+      <c r="B224" t="s">
+        <v>665</v>
+      </c>
+      <c r="C224" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A225" t="s">
+        <v>667</v>
+      </c>
+      <c r="B225" t="s">
+        <v>668</v>
+      </c>
+      <c r="C225" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A226" t="s">
+        <v>670</v>
+      </c>
+      <c r="B226" t="s">
+        <v>671</v>
+      </c>
+      <c r="C226" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A227" t="s">
+        <v>673</v>
+      </c>
+      <c r="B227" t="s">
+        <v>674</v>
+      </c>
+      <c r="C227" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A228" t="s">
+        <v>676</v>
+      </c>
+      <c r="B228" t="s">
+        <v>677</v>
+      </c>
+      <c r="C228" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A229" t="s">
+        <v>679</v>
+      </c>
+      <c r="B229" t="s">
+        <v>680</v>
+      </c>
+      <c r="C229" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A230" t="s">
+        <v>682</v>
+      </c>
+      <c r="B230" t="s">
+        <v>683</v>
+      </c>
+      <c r="C230" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A231" t="s">
+        <v>685</v>
+      </c>
+      <c r="B231" t="s">
+        <v>686</v>
+      </c>
+      <c r="C231" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A232" t="s">
+        <v>688</v>
+      </c>
+      <c r="B232" t="s">
+        <v>689</v>
+      </c>
+      <c r="C232" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A233" t="s">
+        <v>691</v>
+      </c>
+      <c r="B233" t="s">
+        <v>692</v>
+      </c>
+      <c r="C233" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A234" t="s">
+        <v>694</v>
+      </c>
+      <c r="B234" t="s">
+        <v>695</v>
+      </c>
+      <c r="C234" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A235" t="s">
+        <v>697</v>
+      </c>
+      <c r="B235" t="s">
+        <v>698</v>
+      </c>
+      <c r="C235" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A236" t="s">
+        <v>700</v>
+      </c>
+      <c r="B236" t="s">
+        <v>701</v>
+      </c>
+      <c r="C236" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A237" t="s">
+        <v>703</v>
+      </c>
+      <c r="B237" t="s">
+        <v>704</v>
+      </c>
+      <c r="C237" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A238" t="s">
+        <v>706</v>
+      </c>
+      <c r="B238" t="s">
+        <v>707</v>
+      </c>
+      <c r="C238" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A239" t="s">
+        <v>709</v>
+      </c>
+      <c r="B239" t="s">
+        <v>710</v>
+      </c>
+      <c r="C239" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A240" t="s">
+        <v>712</v>
+      </c>
+      <c r="B240" t="s">
+        <v>713</v>
+      </c>
+      <c r="C240" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A241" t="s">
+        <v>715</v>
+      </c>
+      <c r="B241" t="s">
+        <v>716</v>
+      </c>
+      <c r="C241" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A242" t="s">
+        <v>718</v>
+      </c>
+      <c r="B242" t="s">
+        <v>719</v>
+      </c>
+      <c r="C242" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A243" t="s">
+        <v>721</v>
+      </c>
+      <c r="B243" t="s">
+        <v>722</v>
+      </c>
+      <c r="C243" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A244" t="s">
+        <v>724</v>
+      </c>
+      <c r="B244" t="s">
+        <v>725</v>
+      </c>
+      <c r="C244" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A245" t="s">
+        <v>727</v>
+      </c>
+      <c r="B245" t="s">
+        <v>728</v>
+      </c>
+      <c r="C245" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A246" t="s">
+        <v>730</v>
+      </c>
+      <c r="B246" t="s">
+        <v>731</v>
+      </c>
+      <c r="C246" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A247" t="s">
+        <v>733</v>
+      </c>
+      <c r="B247" t="s">
+        <v>734</v>
+      </c>
+      <c r="C247" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A248" t="s">
+        <v>736</v>
+      </c>
+      <c r="B248" t="s">
+        <v>737</v>
+      </c>
+      <c r="C248" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A249" t="s">
+        <v>739</v>
+      </c>
+      <c r="B249" t="s">
+        <v>740</v>
+      </c>
+      <c r="C249" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A250" t="s">
+        <v>742</v>
+      </c>
+      <c r="B250" t="s">
+        <v>743</v>
+      </c>
+      <c r="C250" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A251" t="s">
+        <v>745</v>
+      </c>
+      <c r="B251" t="s">
+        <v>746</v>
+      </c>
+      <c r="C251" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A252" t="s">
+        <v>748</v>
+      </c>
+      <c r="B252" t="s">
+        <v>749</v>
+      </c>
+      <c r="C252" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A253" t="s">
+        <v>751</v>
+      </c>
+      <c r="B253" t="s">
+        <v>752</v>
+      </c>
+      <c r="C253" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A254" t="s">
+        <v>754</v>
+      </c>
+      <c r="B254" t="s">
+        <v>755</v>
+      </c>
+      <c r="C254" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A255" t="s">
+        <v>757</v>
+      </c>
+      <c r="B255" t="s">
+        <v>758</v>
+      </c>
+      <c r="C255" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A256" t="s">
+        <v>760</v>
+      </c>
+      <c r="B256" t="s">
+        <v>761</v>
+      </c>
+      <c r="C256" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A257" t="s">
+        <v>763</v>
+      </c>
+      <c r="B257" t="s">
+        <v>764</v>
+      </c>
+      <c r="C257" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A258" t="s">
+        <v>766</v>
+      </c>
+      <c r="B258" t="s">
+        <v>767</v>
+      </c>
+      <c r="C258" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A259" t="s">
+        <v>769</v>
+      </c>
+      <c r="B259" t="s">
+        <v>770</v>
+      </c>
+      <c r="C259" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A260" t="s">
+        <v>772</v>
+      </c>
+      <c r="B260" t="s">
+        <v>773</v>
+      </c>
+      <c r="C260" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A261" t="s">
+        <v>775</v>
+      </c>
+      <c r="B261" t="s">
+        <v>776</v>
+      </c>
+      <c r="C261" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A262" t="s">
+        <v>778</v>
+      </c>
+      <c r="B262" t="s">
+        <v>779</v>
+      </c>
+      <c r="C262" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A263" t="s">
+        <v>781</v>
+      </c>
+      <c r="B263" t="s">
+        <v>782</v>
+      </c>
+      <c r="C263" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A264" t="s">
+        <v>784</v>
+      </c>
+      <c r="B264" t="s">
+        <v>785</v>
+      </c>
+      <c r="C264" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A265" t="s">
+        <v>787</v>
+      </c>
+      <c r="B265" t="s">
+        <v>788</v>
+      </c>
+      <c r="C265" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A266" t="s">
+        <v>790</v>
+      </c>
+      <c r="B266" t="s">
+        <v>791</v>
+      </c>
+      <c r="C266" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A267" t="s">
+        <v>793</v>
+      </c>
+      <c r="B267" t="s">
+        <v>794</v>
+      </c>
+      <c r="C267" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A268" t="s">
+        <v>796</v>
+      </c>
+      <c r="B268" t="s">
+        <v>797</v>
+      </c>
+      <c r="C268" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A269" t="s">
+        <v>799</v>
+      </c>
+      <c r="B269" t="s">
+        <v>800</v>
+      </c>
+      <c r="C269" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A270" t="s">
+        <v>802</v>
+      </c>
+      <c r="B270" t="s">
+        <v>803</v>
+      </c>
+      <c r="C270" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A271" t="s">
+        <v>805</v>
+      </c>
+      <c r="B271" t="s">
+        <v>806</v>
+      </c>
+      <c r="C271" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A272" t="s">
+        <v>808</v>
+      </c>
+      <c r="B272" t="s">
+        <v>809</v>
+      </c>
+      <c r="C272" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A273" t="s">
+        <v>811</v>
+      </c>
+      <c r="B273" t="s">
+        <v>812</v>
+      </c>
+      <c r="C273" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A274" t="s">
+        <v>814</v>
+      </c>
+      <c r="B274" t="s">
+        <v>815</v>
+      </c>
+      <c r="C274" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A275" t="s">
+        <v>817</v>
+      </c>
+      <c r="B275" t="s">
+        <v>818</v>
+      </c>
+      <c r="C275" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A276" t="s">
+        <v>820</v>
+      </c>
+      <c r="B276" t="s">
+        <v>821</v>
+      </c>
+      <c r="C276" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A277" t="s">
+        <v>823</v>
+      </c>
+      <c r="B277" t="s">
+        <v>824</v>
+      </c>
+      <c r="C277" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A278" t="s">
+        <v>826</v>
+      </c>
+      <c r="B278" t="s">
+        <v>827</v>
+      </c>
+      <c r="C278" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A279" t="s">
+        <v>829</v>
+      </c>
+      <c r="B279" t="s">
+        <v>830</v>
+      </c>
+      <c r="C279" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A280" t="s">
+        <v>832</v>
+      </c>
+      <c r="B280" t="s">
+        <v>833</v>
+      </c>
+      <c r="C280" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A281" t="s">
+        <v>835</v>
+      </c>
+      <c r="B281" t="s">
+        <v>836</v>
+      </c>
+      <c r="C281" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A282" t="s">
+        <v>838</v>
+      </c>
+      <c r="B282" t="s">
+        <v>839</v>
+      </c>
+      <c r="C282" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A283" t="s">
+        <v>841</v>
+      </c>
+      <c r="B283" t="s">
+        <v>842</v>
+      </c>
+      <c r="C283" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A284" t="s">
+        <v>844</v>
+      </c>
+      <c r="B284" t="s">
+        <v>845</v>
+      </c>
+      <c r="C284" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A285" t="s">
+        <v>847</v>
+      </c>
+      <c r="B285" t="s">
+        <v>848</v>
+      </c>
+      <c r="C285" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A286" t="s">
+        <v>850</v>
+      </c>
+      <c r="B286" t="s">
+        <v>851</v>
+      </c>
+      <c r="C286" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A287" t="s">
+        <v>853</v>
+      </c>
+      <c r="B287" t="s">
+        <v>854</v>
+      </c>
+      <c r="C287" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A288" t="s">
+        <v>856</v>
+      </c>
+      <c r="B288" t="s">
+        <v>857</v>
+      </c>
+      <c r="C288" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A289" t="s">
+        <v>859</v>
+      </c>
+      <c r="B289" t="s">
+        <v>860</v>
+      </c>
+      <c r="C289" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A290" t="s">
+        <v>862</v>
+      </c>
+      <c r="B290" t="s">
+        <v>863</v>
+      </c>
+      <c r="C290" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A291" t="s">
+        <v>865</v>
+      </c>
+      <c r="B291" t="s">
+        <v>866</v>
+      </c>
+      <c r="C291" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A292" t="s">
+        <v>868</v>
+      </c>
+      <c r="B292" t="s">
+        <v>869</v>
+      </c>
+      <c r="C292" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A293" t="s">
+        <v>871</v>
+      </c>
+      <c r="B293" t="s">
+        <v>872</v>
+      </c>
+      <c r="C293" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A294" t="s">
+        <v>874</v>
+      </c>
+      <c r="B294" t="s">
+        <v>875</v>
+      </c>
+      <c r="C294" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A295" t="s">
+        <v>877</v>
+      </c>
+      <c r="B295" t="s">
+        <v>169</v>
+      </c>
+      <c r="C295" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A296" t="s">
+        <v>878</v>
+      </c>
+      <c r="B296" t="s">
+        <v>879</v>
+      </c>
+      <c r="C296" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A297" t="s">
+        <v>881</v>
+      </c>
+      <c r="B297" t="s">
+        <v>882</v>
+      </c>
+      <c r="C297" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A298" t="s">
+        <v>884</v>
+      </c>
+      <c r="B298" t="s">
+        <v>885</v>
+      </c>
+      <c r="C298" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A299" t="s">
+        <v>887</v>
+      </c>
+      <c r="B299" t="s">
+        <v>888</v>
+      </c>
+      <c r="C299" t="s">
+        <v>889</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/database/temp_outputs/combined_chunks_file.xlsx
+++ b/src/database/temp_outputs/combined_chunks_file.xlsx
@@ -1,84 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repositories\XpressCredentialling\src\database\temp_outputs\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{021AF42D-CA74-440F-B714-57CAFBF3306F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
-  <si>
-    <t>National Provider Identifier</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>1427085877</t>
-  </si>
-  <si>
-    <t>GRANT SEARLES</t>
-  </si>
-  <si>
-    <t>grantsearles@hotmail.com</t>
-  </si>
-  <si>
-    <t>1497844617</t>
-  </si>
-  <si>
-    <t>DAVID MILLER</t>
-  </si>
-  <si>
-    <t>David.Miller@UTSouthwestern.edu</t>
-  </si>
-  <si>
-    <t>1689630188</t>
-  </si>
-  <si>
-    <t>JOHN MATHEWS</t>
-  </si>
-  <si>
-    <t>michelle.mcclinton@bhsala.com</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -93,43 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -417,52 +420,80 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>National Provider Identifier</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1689630188</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>JOHN MATHEWS</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>michelle.mcclinton@bhsala.com</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1497844617</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>DAVID MILLER</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>David.Miller@UTSouthwestern.edu</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1427085877</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GRANT SEARLES</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>grantsearles@hotmail.com</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/src/database/temp_outputs/combined_chunks_file.xlsx
+++ b/src/database/temp_outputs/combined_chunks_file.xlsx
@@ -1,37 +1,102 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repositories\XpressCredentialling\src\database\temp_outputs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12747A20-6A26-4F81-8FBD-8D6C8CE20A0A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+  <si>
+    <t>National Provider Identifier</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>1427085877</t>
+  </si>
+  <si>
+    <t>GRANT SEARLES</t>
+  </si>
+  <si>
+    <t>grantsearles@hotmail.com</t>
+  </si>
+  <si>
+    <t>1497844617</t>
+  </si>
+  <si>
+    <t>DAVID MILLER</t>
+  </si>
+  <si>
+    <t>David.Miller@UTSouthwestern.edu</t>
+  </si>
+  <si>
+    <t>1689630188</t>
+  </si>
+  <si>
+    <t>JOHN MATHEWS</t>
+  </si>
+  <si>
+    <t>michelle.mcclinton@bhsala.com</t>
+  </si>
+  <si>
+    <t>1083678858</t>
+  </si>
+  <si>
+    <t>GREGORY DUNN</t>
+  </si>
+  <si>
+    <t>Gregory.Dunn@allina.com</t>
+  </si>
+  <si>
+    <t>1184693400</t>
+  </si>
+  <si>
+    <t>JOHN ABT</t>
+  </si>
+  <si>
+    <t>JLAEM@bellsouth.net</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +111,43 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,80 +435,79 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="19.6640625" customWidth="1"/>
+    <col min="2" max="2" width="23" customWidth="1"/>
+    <col min="3" max="3" width="30.88671875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>National Provider Identifier</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1689630188</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>JOHN MATHEWS</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>michelle.mcclinton@bhsala.com</t>
-        </is>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1497844617</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>DAVID MILLER</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>David.Miller@UTSouthwestern.edu</t>
-        </is>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1427085877</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>GRANT SEARLES</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>grantsearles@hotmail.com</t>
-        </is>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/src/database/temp_outputs/combined_chunks_file.xlsx
+++ b/src/database/temp_outputs/combined_chunks_file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repositories\XpressCredentialling\src\database\temp_outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12747A20-6A26-4F81-8FBD-8D6C8CE20A0A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67AD7772-C939-4C53-BDB0-0719859F7F01}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="81">
   <si>
     <t>National Provider Identifier</t>
   </si>
@@ -31,40 +31,22 @@
     <t>Email</t>
   </si>
   <si>
-    <t>1427085877</t>
-  </si>
-  <si>
-    <t>GRANT SEARLES</t>
-  </si>
-  <si>
-    <t>grantsearles@hotmail.com</t>
-  </si>
-  <si>
-    <t>1497844617</t>
-  </si>
-  <si>
-    <t>DAVID MILLER</t>
-  </si>
-  <si>
-    <t>David.Miller@UTSouthwestern.edu</t>
-  </si>
-  <si>
-    <t>1689630188</t>
-  </si>
-  <si>
-    <t>JOHN MATHEWS</t>
-  </si>
-  <si>
-    <t>michelle.mcclinton@bhsala.com</t>
-  </si>
-  <si>
-    <t>1083678858</t>
-  </si>
-  <si>
-    <t>GREGORY DUNN</t>
-  </si>
-  <si>
-    <t>Gregory.Dunn@allina.com</t>
+    <t>1013914100</t>
+  </si>
+  <si>
+    <t>BEATRIX ARAIZA</t>
+  </si>
+  <si>
+    <t>trix155@hotmail.com</t>
+  </si>
+  <si>
+    <t>1578511861</t>
+  </si>
+  <si>
+    <t>MUHAMMAD HIZKIL</t>
+  </si>
+  <si>
+    <t>ayazhizkil@gmail.com</t>
   </si>
   <si>
     <t>1184693400</t>
@@ -74,6 +56,213 @@
   </si>
   <si>
     <t>JLAEM@bellsouth.net</t>
+  </si>
+  <si>
+    <t>1497794739</t>
+  </si>
+  <si>
+    <t>WAYNE BARRY</t>
+  </si>
+  <si>
+    <t>edpdoc@aol.com</t>
+  </si>
+  <si>
+    <t>1700862414</t>
+  </si>
+  <si>
+    <t>HECTOR LABRADA</t>
+  </si>
+  <si>
+    <t>liubilabra1@bellsouth.net</t>
+  </si>
+  <si>
+    <t>1467499285</t>
+  </si>
+  <si>
+    <t>JORGE SANTANDER</t>
+  </si>
+  <si>
+    <t>santander_MD@yahoo.com</t>
+  </si>
+  <si>
+    <t>1104875178</t>
+  </si>
+  <si>
+    <t>MARIANELA DE LA PORTILLA</t>
+  </si>
+  <si>
+    <t>nelyportilla@aol.com</t>
+  </si>
+  <si>
+    <t>1740373406</t>
+  </si>
+  <si>
+    <t>OFILIO ARGUELLO</t>
+  </si>
+  <si>
+    <t>darguell@bellsouth.net</t>
+  </si>
+  <si>
+    <t>1851528335</t>
+  </si>
+  <si>
+    <t>ERICH GERHARDT</t>
+  </si>
+  <si>
+    <t>Erich.gerhardt1@gmail.com</t>
+  </si>
+  <si>
+    <t>1093841728</t>
+  </si>
+  <si>
+    <t>DENNIS ROBISON</t>
+  </si>
+  <si>
+    <t>d.robison50@gmail.com</t>
+  </si>
+  <si>
+    <t>1437460854</t>
+  </si>
+  <si>
+    <t>JOHN HAGEDORN</t>
+  </si>
+  <si>
+    <t>Johnhagedorn@gmail.com</t>
+  </si>
+  <si>
+    <t>1790076826</t>
+  </si>
+  <si>
+    <t>ELISABETH JONES BROWN</t>
+  </si>
+  <si>
+    <t>raeraegomez@gmail.com</t>
+  </si>
+  <si>
+    <t>1790912228</t>
+  </si>
+  <si>
+    <t>TRAVIS HOLLOWAY</t>
+  </si>
+  <si>
+    <t>Travis.holloway2@hcahealthcare.com</t>
+  </si>
+  <si>
+    <t>1710274147</t>
+  </si>
+  <si>
+    <t>MICHAEL VAN HAL</t>
+  </si>
+  <si>
+    <t>vanvlietplasticsurgery@gmail.com</t>
+  </si>
+  <si>
+    <t>1003060211</t>
+  </si>
+  <si>
+    <t>VICHIN PURI</t>
+  </si>
+  <si>
+    <t>vichinpuri@mhd.com</t>
+  </si>
+  <si>
+    <t>1518910918</t>
+  </si>
+  <si>
+    <t>RAMON SASTRE</t>
+  </si>
+  <si>
+    <t>rafenuv@aol.com</t>
+  </si>
+  <si>
+    <t>1356436786</t>
+  </si>
+  <si>
+    <t>HUMBERTO FERNANDEZ-MIRO</t>
+  </si>
+  <si>
+    <t>mesmiro@gmail.com</t>
+  </si>
+  <si>
+    <t>1386646008</t>
+  </si>
+  <si>
+    <t>JAMES SCHUMACHER</t>
+  </si>
+  <si>
+    <t>april@sarasotaneurosurgery.com</t>
+  </si>
+  <si>
+    <t>1821046079</t>
+  </si>
+  <si>
+    <t>ALVARO OCAMPO</t>
+  </si>
+  <si>
+    <t>alomed@gmail.com</t>
+  </si>
+  <si>
+    <t>1669433801</t>
+  </si>
+  <si>
+    <t>TIMOTHY STERNBERG</t>
+  </si>
+  <si>
+    <t>timothy.l.sternberg.ctr@mail.mil</t>
+  </si>
+  <si>
+    <t>1073525747</t>
+  </si>
+  <si>
+    <t>PASQUALE DELL'API</t>
+  </si>
+  <si>
+    <t>dellapipx@yahoo.com</t>
+  </si>
+  <si>
+    <t>1689772881</t>
+  </si>
+  <si>
+    <t>MATTHEW DEMETREE</t>
+  </si>
+  <si>
+    <t>drmdemetree@bellsouth.net</t>
+  </si>
+  <si>
+    <t>1831170240</t>
+  </si>
+  <si>
+    <t>PEDRO TIRADO</t>
+  </si>
+  <si>
+    <t>pwtirado@me.com</t>
+  </si>
+  <si>
+    <t>1417945098</t>
+  </si>
+  <si>
+    <t>AVELINO CARIDE</t>
+  </si>
+  <si>
+    <t>gocanes83@att.net</t>
+  </si>
+  <si>
+    <t>1831175702</t>
+  </si>
+  <si>
+    <t>FRANCISCO ALVAREZ-GIL</t>
+  </si>
+  <si>
+    <t>falvarezgil@me.com</t>
+  </si>
+  <si>
+    <t>1346294337</t>
+  </si>
+  <si>
+    <t>EMMANUEL ROLDAN</t>
+  </si>
+  <si>
+    <t>eroldan65@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -138,7 +327,98 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="9">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -436,12 +716,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" customWidth="1"/>
-    <col min="2" max="2" width="23" customWidth="1"/>
-    <col min="3" max="3" width="30.88671875" customWidth="1"/>
+    <col min="1" max="1" width="17.44140625" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -510,7 +789,243 @@
         <v>17</v>
       </c>
     </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>63</v>
+      </c>
+      <c r="B22" t="s">
+        <v>64</v>
+      </c>
+      <c r="C22" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>66</v>
+      </c>
+      <c r="B23" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>69</v>
+      </c>
+      <c r="B24" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>72</v>
+      </c>
+      <c r="B25" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>75</v>
+      </c>
+      <c r="B26" t="s">
+        <v>76</v>
+      </c>
+      <c r="C26" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>78</v>
+      </c>
+      <c r="B27" t="s">
+        <v>79</v>
+      </c>
+      <c r="C27" t="s">
+        <v>80</v>
+      </c>
+    </row>
   </sheetData>
+  <conditionalFormatting sqref="A1:XFD1048576">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>